--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -250,9 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Prescription
@@ -595,6 +595,9 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
+    <t>1540: fixed value = plan when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
+  </si>
+  <si>
     <t>Request.intent</t>
   </si>
   <si>
@@ -602,9 +605,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1540: fixed value = plan when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
   </si>
   <si>
     <t>MedicationRequest.category</t>
@@ -2290,12 +2290,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="128.41796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2528,16 +2528,16 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>82</v>
@@ -3132,10 +3132,10 @@
         <v>82</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -3252,10 +3252,10 @@
         <v>82</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3372,10 +3372,10 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3494,10 +3494,10 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3608,22 +3608,22 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3728,19 +3728,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3848,16 +3848,16 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3971,19 +3971,19 @@
         <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -4089,16 +4089,16 @@
         <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AN15" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="AO15" t="s" s="2">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -4211,16 +4211,16 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="AO16" t="s" s="2">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -4326,19 +4326,19 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4452,10 +4452,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4568,10 +4568,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4682,22 +4682,22 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4800,22 +4800,22 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4920,22 +4920,22 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -5040,22 +5040,22 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5158,19 +5158,19 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5276,22 +5276,22 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5394,19 +5394,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5512,19 +5512,19 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5632,16 +5632,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5756,13 +5756,13 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5870,22 +5870,22 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5990,19 +5990,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6108,16 +6108,16 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6232,10 +6232,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6344,16 +6344,16 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6464,16 +6464,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6590,10 +6590,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6702,16 +6702,16 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6820,16 +6820,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6940,16 +6940,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7064,10 +7064,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7184,10 +7184,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7306,10 +7306,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7426,16 +7426,16 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7546,16 +7546,16 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7668,16 +7668,16 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7786,16 +7786,16 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7908,10 +7908,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8028,16 +8028,16 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8150,16 +8150,16 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8270,16 +8270,16 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8392,16 +8392,16 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AN51" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8516,10 +8516,10 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -8628,10 +8628,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8748,10 +8748,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8874,10 +8874,10 @@
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8990,16 +8990,16 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AN56" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9112,16 +9112,16 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9234,16 +9234,16 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AN58" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9356,10 +9356,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9476,10 +9476,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9591,13 +9591,13 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9712,10 +9712,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9832,10 +9832,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9954,10 +9954,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10074,10 +10074,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10192,10 +10192,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10312,10 +10312,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10434,10 +10434,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10552,10 +10552,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10670,10 +10670,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10788,10 +10788,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10907,13 +10907,13 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11027,19 +11027,19 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AN73" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11145,19 +11145,19 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -11265,13 +11265,13 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11386,13 +11386,13 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -11501,13 +11501,13 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11622,10 +11622,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11742,10 +11742,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11864,10 +11864,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11981,19 +11981,19 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="82" hidden="true">
@@ -12099,19 +12099,19 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AN82" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -12214,16 +12214,16 @@
         <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AL83" t="s" s="2">
+      <c r="AM83" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12340,10 +12340,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12454,16 +12454,16 @@
         <v>103</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="AL85" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$90</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3439" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -438,38 +438,139 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:medicationrequest-recordedLocation</t>
+  </si>
+  <si>
+    <t>medicationrequest-recordedLocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://va.gov/fhir/StructureDefinition/medicationrequest-recordedLocation}
+</t>
+  </si>
+  <si>
+    <t>Extension medicationrequest-recordedLocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:medicationrequest-recordedLocation.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:medicationrequest-recordedLocation.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:medicationrequest-recordedLocation.url</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/StructureDefinition/medicationrequest-recordedLocation</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:medicationrequest-recordedLocation.value[x]</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>1765: reference from NON-VA MEDS - CLINIC (#55.05-13)</t>
+  </si>
+  <si>
+    <t>MedicationRequest.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -627,9 +728,6 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -1131,6 +1229,9 @@
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
   </si>
   <si>
+    <t>1764: source value from NON-VA MEDS - DISCLAIMER (#55.05-10)</t>
+  </si>
+  <si>
     <t>Request.note</t>
   </si>
   <si>
@@ -1165,36 +1266,13 @@
     <t>MedicationRequest.dosageInstruction.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.dosageInstruction.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.modifierExtension</t>
@@ -2252,12 +2330,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP85"/>
+  <dimension ref="A1:AP90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.27734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="72.23046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="61.27734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="34.953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3273,7 +3351,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3292,17 +3370,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3339,16 +3415,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -3375,7 +3449,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3389,43 +3463,41 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3473,7 +3545,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3482,7 +3554,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3497,7 +3569,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3511,7 +3583,7 @@
         <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3522,7 +3594,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
@@ -3534,17 +3606,15 @@
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>152</v>
       </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3593,45 +3663,45 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AN11" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="AO11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3639,32 +3709,30 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3689,58 +3757,58 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3748,10 +3816,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3759,7 +3827,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>91</v>
@@ -3774,16 +3842,16 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3791,7 +3859,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>82</v>
@@ -3809,13 +3877,13 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>82</v>
@@ -3833,10 +3901,10 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>91</v>
@@ -3845,19 +3913,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3868,10 +3936,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3879,7 +3947,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>91</v>
@@ -3888,23 +3956,21 @@
         <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3929,13 +3995,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3953,10 +4019,10 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>91</v>
@@ -3968,19 +4034,19 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3988,14 +4054,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4005,27 +4071,29 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4049,29 +4117,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4083,7 +4153,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4092,13 +4162,13 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -4106,14 +4176,12 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>82</v>
       </c>
@@ -4125,7 +4193,7 @@
         <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -4134,16 +4202,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4169,13 +4237,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4193,7 +4261,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4211,27 +4279,27 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>188</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>82</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4239,16 +4307,16 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>92</v>
@@ -4257,12 +4325,14 @@
         <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4287,13 +4357,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4311,10 +4381,10 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>91</v>
@@ -4329,16 +4399,16 @@
         <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4346,10 +4416,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4366,22 +4436,22 @@
         <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4407,13 +4477,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -4431,7 +4501,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4449,13 +4519,13 @@
         <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4466,10 +4536,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4477,7 +4547,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4486,21 +4556,23 @@
         <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4525,32 +4597,34 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AC19" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>91</v>
@@ -4562,19 +4636,19 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4582,14 +4656,12 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4598,7 +4670,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>92</v>
@@ -4607,18 +4679,20 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4643,37 +4717,35 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4682,19 +4754,19 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4702,21 +4774,23 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>92</v>
@@ -4725,19 +4799,19 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4763,11 +4837,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4785,13 +4861,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4803,27 +4879,27 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4831,13 +4907,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
@@ -4846,17 +4922,15 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4881,13 +4955,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4905,10 +4979,10 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>91</v>
@@ -4923,27 +4997,27 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4957,25 +5031,25 @@
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5025,7 +5099,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5043,27 +5117,27 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5074,25 +5148,25 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5131,25 +5205,23 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5161,16 +5233,16 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5178,12 +5250,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5204,13 +5278,13 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5261,7 +5335,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5276,30 +5350,30 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5322,15 +5396,17 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5355,13 +5431,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5379,10 +5453,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>91</v>
@@ -5397,27 +5471,27 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5425,30 +5499,32 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5497,10 +5573,10 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>91</v>
@@ -5515,27 +5591,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5549,25 +5625,25 @@
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>279</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5593,13 +5669,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5617,7 +5693,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5635,27 +5711,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5666,7 +5742,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5678,13 +5754,13 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5735,13 +5811,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5753,16 +5829,16 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5770,10 +5846,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5784,29 +5860,27 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
+        <v>294</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5831,13 +5905,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5855,13 +5929,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5873,27 +5947,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5901,32 +5975,30 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5975,13 +6047,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5993,13 +6065,13 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>307</v>
@@ -6010,10 +6082,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6024,7 +6096,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6033,16 +6105,16 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6093,13 +6165,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -6111,16 +6183,16 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6128,10 +6200,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6142,7 +6214,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6154,15 +6226,17 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6187,13 +6261,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6211,13 +6285,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -6229,13 +6303,13 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6246,10 +6320,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6260,7 +6334,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6269,16 +6343,16 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6329,13 +6403,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6347,16 +6421,16 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6364,10 +6438,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6378,7 +6452,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6387,21 +6461,21 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>334</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6425,13 +6499,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6449,13 +6523,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6470,24 +6544,24 @@
         <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6498,7 +6572,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6510,16 +6584,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>341</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6545,13 +6619,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6569,13 +6643,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -6587,16 +6661,16 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6604,10 +6678,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6627,16 +6701,16 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6687,7 +6761,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6705,13 +6779,13 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6722,10 +6796,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6745,16 +6819,16 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>351</v>
+        <v>105</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6805,7 +6879,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6823,13 +6897,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6840,10 +6914,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6857,26 +6931,24 @@
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J39" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>361</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6925,7 +6997,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6943,13 +7015,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6960,10 +7032,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6983,19 +7055,21 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7043,7 +7117,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7055,19 +7129,19 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7078,21 +7152,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7104,16 +7178,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7139,55 +7213,55 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7205,7 +7279,7 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7218,13 +7292,13 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>376</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>377</v>
@@ -7232,12 +7306,8 @@
       <c r="M42" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7285,7 +7355,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7297,19 +7367,19 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>134</v>
+        <v>380</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7320,10 +7390,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7334,30 +7404,28 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7405,13 +7473,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7420,30 +7488,30 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7454,7 +7522,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>92</v>
@@ -7463,21 +7531,21 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7525,13 +7593,13 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
@@ -7543,27 +7611,27 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7574,7 +7642,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7583,23 +7651,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>151</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7623,13 +7687,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7647,19 +7711,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>401</v>
+        <v>153</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7671,32 +7735,32 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>386</v>
+        <v>154</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7705,18 +7769,20 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>365</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7753,31 +7819,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>158</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7789,56 +7855,56 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>386</v>
+        <v>154</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>408</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>411</v>
+        <v>177</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>412</v>
+        <v>178</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7887,19 +7953,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7911,7 +7977,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>414</v>
+        <v>134</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7922,10 +7988,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7948,18 +8014,18 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7983,13 +8049,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8007,7 +8073,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8031,21 +8097,21 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8059,7 +8125,7 @@
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
@@ -8068,19 +8134,17 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8105,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8129,7 +8193,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8153,21 +8217,21 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>434</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8178,7 +8242,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8190,17 +8254,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8225,13 +8291,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8249,13 +8315,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8273,21 +8339,21 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>443</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8310,20 +8376,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8347,13 +8409,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8371,7 +8433,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8395,21 +8457,21 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>452</v>
+        <v>411</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8420,7 +8482,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8432,16 +8494,20 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8489,13 +8555,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8513,21 +8579,21 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8547,18 +8613,20 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>365</v>
+        <v>441</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>366</v>
+        <v>442</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8583,13 +8651,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8607,7 +8675,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>368</v>
+        <v>447</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8619,7 +8687,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8631,32 +8699,32 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>369</v>
+        <v>448</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8665,21 +8733,23 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>138</v>
+        <v>451</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
+        <v>452</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8703,43 +8773,43 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>374</v>
+        <v>457</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8751,21 +8821,21 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>369</v>
+        <v>458</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8788,17 +8858,17 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8823,31 +8893,31 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8871,21 +8941,21 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8908,19 +8978,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8945,13 +9015,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8993,21 +9063,21 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9018,7 +9088,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9030,20 +9100,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N57" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="O57" t="s" s="2">
-        <v>483</v>
-      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9091,13 +9157,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9115,21 +9181,21 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9149,23 +9215,19 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>488</v>
+        <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>489</v>
+        <v>151</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9213,7 +9275,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>493</v>
+        <v>153</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9225,7 +9287,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9237,32 +9299,32 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>494</v>
+        <v>154</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9271,23 +9333,21 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>497</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>498</v>
+        <v>398</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9323,31 +9383,31 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>502</v>
+        <v>158</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9359,7 +9419,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>503</v>
+        <v>154</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9370,10 +9430,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9396,17 +9456,17 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>497</v>
+        <v>202</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9431,13 +9491,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9455,7 +9515,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9479,21 +9539,21 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9513,19 +9573,23 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9573,7 +9637,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9594,24 +9658,24 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9631,19 +9695,23 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>365</v>
+        <v>504</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>366</v>
+        <v>505</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9691,7 +9759,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>368</v>
+        <v>509</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9703,7 +9771,7 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9715,32 +9783,32 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>369</v>
+        <v>510</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9749,21 +9817,23 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>513</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>138</v>
+        <v>514</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>371</v>
+        <v>515</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9811,19 +9881,19 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>374</v>
+        <v>518</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9835,56 +9905,56 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>522</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>377</v>
+        <v>523</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>378</v>
+        <v>524</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>140</v>
+        <v>525</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>146</v>
+        <v>526</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9933,19 +10003,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>379</v>
+        <v>527</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9957,7 +10027,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>134</v>
+        <v>528</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9968,10 +10038,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9991,21 +10061,21 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10053,7 +10123,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10077,7 +10147,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10088,10 +10158,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10114,13 +10184,13 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>365</v>
+        <v>535</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>366</v>
+        <v>536</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>367</v>
+        <v>537</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10171,7 +10241,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>368</v>
+        <v>534</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10183,7 +10253,7 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10192,10 +10262,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>369</v>
+        <v>539</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10206,21 +10276,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10232,17 +10302,15 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10291,19 +10359,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>153</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10315,7 +10383,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>369</v>
+        <v>154</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10326,14 +10394,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>376</v>
+        <v>174</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10346,26 +10414,24 @@
         <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10413,7 +10479,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>379</v>
+        <v>158</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10437,7 +10503,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10448,42 +10514,46 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>497</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>527</v>
+        <v>402</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10531,19 +10601,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>526</v>
+        <v>404</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10555,7 +10625,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>529</v>
+        <v>134</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10566,10 +10636,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10592,15 +10662,17 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10649,7 +10721,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10673,7 +10745,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10684,10 +10756,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10710,13 +10782,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>531</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>536</v>
+        <v>151</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>537</v>
+        <v>152</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10767,7 +10839,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>535</v>
+        <v>153</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10779,7 +10851,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10791,7 +10863,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>534</v>
+        <v>154</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10802,21 +10874,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10828,20 +10900,18 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>539</v>
+        <v>136</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>540</v>
+        <v>398</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>541</v>
+        <v>399</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10889,19 +10959,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>538</v>
+        <v>158</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10910,10 +10980,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>545</v>
+        <v>154</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10924,44 +10994,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>547</v>
+        <v>136</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>548</v>
+        <v>402</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>549</v>
+        <v>403</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11009,19 +11081,19 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>546</v>
+        <v>404</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11030,24 +11102,24 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>552</v>
+        <v>134</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11070,13 +11142,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11127,7 +11199,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11148,24 +11220,24 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>557</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11188,17 +11260,15 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11247,7 +11317,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11268,10 +11338,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11282,10 +11352,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11308,13 +11378,13 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11365,7 +11435,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11389,10 +11459,10 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -11400,10 +11470,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11426,16 +11496,20 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>510</v>
+        <v>564</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11483,7 +11557,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11504,10 +11578,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11518,10 +11592,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11544,15 +11618,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>365</v>
+        <v>572</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>366</v>
+        <v>573</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11601,7 +11677,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>368</v>
+        <v>571</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11613,7 +11689,7 @@
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11622,35 +11698,35 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>369</v>
+        <v>577</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11662,17 +11738,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>137</v>
+        <v>522</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>138</v>
+        <v>580</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11721,19 +11795,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>374</v>
+        <v>579</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11742,60 +11816,58 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>369</v>
+        <v>583</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>137</v>
+        <v>556</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>377</v>
+        <v>586</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>378</v>
+        <v>587</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11843,19 +11915,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>379</v>
+        <v>585</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11864,10 +11936,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>134</v>
+        <v>590</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11878,10 +11950,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11889,7 +11961,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>91</v>
@@ -11904,17 +11976,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>416</v>
+        <v>592</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11939,13 +12009,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>584</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -11963,10 +12033,10 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>91</v>
@@ -11984,24 +12054,24 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>574</v>
+        <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12024,13 +12094,13 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>170</v>
+        <v>535</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12057,13 +12127,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12081,7 +12151,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12102,24 +12172,24 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12142,13 +12212,13 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>596</v>
+        <v>150</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>597</v>
+        <v>151</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>598</v>
+        <v>152</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12199,7 +12269,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>595</v>
+        <v>153</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12211,19 +12281,19 @@
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>600</v>
+        <v>154</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12234,14 +12304,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>602</v>
+        <v>174</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12260,16 +12330,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>603</v>
+        <v>136</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>604</v>
+        <v>398</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>605</v>
+        <v>399</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>606</v>
+        <v>177</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12319,7 +12389,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>601</v>
+        <v>158</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12331,7 +12401,7 @@
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12343,7 +12413,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>607</v>
+        <v>154</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12354,14 +12424,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12374,24 +12444,26 @@
         <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>609</v>
+        <v>136</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>610</v>
+        <v>402</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>611</v>
+        <v>403</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12439,7 +12511,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>608</v>
+        <v>404</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12451,29 +12523,625 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AK86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP85" t="s" s="2">
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
+  <autoFilter ref="A1:AP90">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12483,7 +13151,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI89">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NON (#55.05) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file NON (55.05) to us-core-medicationrequest</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -556,7 +556,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1765: reference from NON-VA MEDS - CLINIC (#55.05-13)</t>
+    <t>1765: reference from NON-VA MEDS - CLINIC (55.05-13)</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -699,7 +699,7 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
-    <t>1540: fixed value = plan when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
+    <t>1540: fixed value = #plan when NON-VA MEDS - ORDER NUMBER (55.05-7) case Not null</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -821,7 +821,7 @@
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>1347: fixed value = true when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
+    <t>1347: fixed value = true when NON-VA MEDS - ORDER NUMBER (55.05-7) case Not null</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
@@ -1232,7 +1232,7 @@
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
   </si>
   <si>
-    <t>1764: source value from NON-VA MEDS - DISCLAIMER (#55.05-10)</t>
+    <t>1764: source value from NON-VA MEDS - DISCLAIMER (55.05-10)</t>
   </si>
   <si>
     <t>Request.note</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NON (55.05) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file NON-VA MEDS (55.05) to us-core-medicationrequest</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3529" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3529" uniqueCount="643">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t>1765: reference from NON-VA MEDS - CLINIC (55.05-13)</t>
+  </si>
+  <si>
+    <t>NonVAMed.NonVAMed.LocationIEN</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -700,6 +703,9 @@
   </si>
   <si>
     <t>1540: fixed value = #plan when NON-VA MEDS - ORDER NUMBER (55.05-7) case Not null</t>
+  </si>
+  <si>
+    <t>NonVAMed.NonVAMed.CPRSOrderIEN</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -4080,7 +4086,7 @@
         <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>83</v>
@@ -4100,14 +4106,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4129,16 +4135,16 @@
         <v>137</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
@@ -4187,7 +4193,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4225,10 +4231,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4251,16 +4257,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4310,7 +4316,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4331,27 +4337,27 @@
         <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4377,13 +4383,13 @@
         <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4409,13 +4415,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4433,7 +4439,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>92</v>
@@ -4454,16 +4460,16 @@
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>83</v>
@@ -4471,10 +4477,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4497,16 +4503,16 @@
         <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4532,13 +4538,13 @@
         <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>83</v>
@@ -4556,7 +4562,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4577,13 +4583,13 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4594,10 +4600,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4623,13 +4629,13 @@
         <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4655,13 +4661,13 @@
         <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
@@ -4679,7 +4685,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>92</v>
@@ -4694,22 +4700,22 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
@@ -4717,10 +4723,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4743,16 +4749,16 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4778,19 +4784,19 @@
         <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
@@ -4800,7 +4806,7 @@
         <v>141</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4824,13 +4830,13 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>83</v>
@@ -4838,13 +4844,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>83</v>
@@ -4866,16 +4872,16 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4901,13 +4907,13 @@
         <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
@@ -4925,7 +4931,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4949,13 +4955,13 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
@@ -4963,10 +4969,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4992,10 +4998,10 @@
         <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5022,13 +5028,13 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -5046,7 +5052,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5067,16 +5073,16 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
@@ -5084,10 +5090,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5110,16 +5116,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5169,7 +5175,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5196,7 +5202,7 @@
         <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -5207,10 +5213,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5233,13 +5239,13 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5278,7 +5284,7 @@
         <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
@@ -5288,7 +5294,7 @@
         <v>141</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5315,7 +5321,7 @@
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -5326,13 +5332,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>83</v>
@@ -5354,13 +5360,13 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5411,7 +5417,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5426,10 +5432,10 @@
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>83</v>
@@ -5438,7 +5444,7 @@
         <v>83</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5449,10 +5455,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5475,16 +5481,16 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5510,11 +5516,11 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5532,7 +5538,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5553,27 +5559,27 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5596,16 +5602,16 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5655,7 +5661,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>92</v>
@@ -5676,27 +5682,27 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5719,16 +5725,16 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5778,7 +5784,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5799,27 +5805,27 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5842,13 +5848,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5899,7 +5905,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5920,16 +5926,16 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5937,10 +5943,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5963,13 +5969,13 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6020,7 +6026,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6041,27 +6047,27 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6084,13 +6090,13 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6141,7 +6147,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6162,16 +6168,16 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6179,10 +6185,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6205,13 +6211,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6262,7 +6268,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6283,16 +6289,16 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6300,10 +6306,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6326,16 +6332,16 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6361,13 +6367,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6385,7 +6391,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6406,13 +6412,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6423,10 +6429,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6449,13 +6455,13 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6506,7 +6512,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6533,10 +6539,10 @@
         <v>83</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6544,10 +6550,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6570,16 +6576,16 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6605,13 +6611,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6629,7 +6635,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6650,27 +6656,27 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6693,16 +6699,16 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6752,7 +6758,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6773,16 +6779,16 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6790,10 +6796,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6816,13 +6822,13 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6873,7 +6879,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6894,13 +6900,13 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6911,10 +6917,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6940,10 +6946,10 @@
         <v>106</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6994,7 +7000,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7021,7 +7027,7 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7032,10 +7038,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7058,13 +7064,13 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7115,7 +7121,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7136,13 +7142,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7153,10 +7159,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7179,17 +7185,17 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7238,7 +7244,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7259,13 +7265,13 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7276,10 +7282,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7302,16 +7308,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7337,13 +7343,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7361,7 +7367,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7388,7 +7394,7 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7399,10 +7405,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7425,13 +7431,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7482,7 +7488,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7503,13 +7509,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7520,10 +7526,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7546,13 +7552,13 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7603,7 +7609,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7618,19 +7624,19 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7641,10 +7647,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7667,16 +7673,16 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7726,7 +7732,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7747,13 +7753,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7764,10 +7770,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7885,14 +7891,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7914,13 +7920,13 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8008,14 +8014,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8037,16 +8043,16 @@
         <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -8095,7 +8101,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8133,10 +8139,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8159,17 +8165,17 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8218,7 +8224,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8245,21 +8251,21 @@
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8285,14 +8291,14 @@
         <v>151</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8341,7 +8347,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8368,21 +8374,21 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8405,19 +8411,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8442,13 +8448,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8466,7 +8472,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8493,21 +8499,21 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8533,10 +8539,10 @@
         <v>151</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8587,7 +8593,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8614,21 +8620,21 @@
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8651,19 +8657,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8712,7 +8718,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8739,7 +8745,7 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8750,10 +8756,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8776,16 +8782,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8811,13 +8817,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8835,7 +8841,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8862,21 +8868,21 @@
         <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8899,19 +8905,19 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8936,13 +8942,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8960,7 +8966,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8987,21 +8993,21 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9024,17 +9030,17 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9059,13 +9065,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -9083,7 +9089,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9110,21 +9116,21 @@
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9147,19 +9153,19 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9184,13 +9190,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -9208,7 +9214,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9235,21 +9241,21 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9272,13 +9278,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9329,7 +9335,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9362,15 +9368,15 @@
         <v>83</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9488,14 +9494,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9517,13 +9523,13 @@
         <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9611,10 +9617,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9637,17 +9643,17 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9672,13 +9678,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9696,7 +9702,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9729,15 +9735,15 @@
         <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9760,19 +9766,19 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9821,7 +9827,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9848,21 +9854,21 @@
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9885,19 +9891,19 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9946,7 +9952,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9973,21 +9979,21 @@
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10010,19 +10016,19 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10071,7 +10077,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10098,21 +10104,21 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10135,19 +10141,19 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10196,7 +10202,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10223,7 +10229,7 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10234,10 +10240,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10260,17 +10266,17 @@
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10319,7 +10325,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10346,7 +10352,7 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10357,10 +10363,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10383,13 +10389,13 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10440,7 +10446,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10464,10 +10470,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10478,10 +10484,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10599,14 +10605,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10628,13 +10634,13 @@
         <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10722,14 +10728,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10751,16 +10757,16 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10809,7 +10815,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10847,10 +10853,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10873,16 +10879,16 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10932,7 +10938,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10959,7 +10965,7 @@
         <v>83</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10970,10 +10976,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11091,14 +11097,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11120,13 +11126,13 @@
         <v>137</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11214,14 +11220,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11243,16 +11249,16 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11301,7 +11307,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11339,10 +11345,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11365,13 +11371,13 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11422,7 +11428,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11449,7 +11455,7 @@
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -11460,10 +11466,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11486,13 +11492,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11543,7 +11549,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11570,7 +11576,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -11581,10 +11587,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11607,13 +11613,13 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11664,7 +11670,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11691,7 +11697,7 @@
         <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -11702,10 +11708,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11728,19 +11734,19 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11789,7 +11795,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11813,10 +11819,10 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>83</v>
@@ -11827,10 +11833,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11853,16 +11859,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11912,7 +11918,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11936,24 +11942,24 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11976,13 +11982,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12033,7 +12039,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12057,24 +12063,24 @@
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12097,16 +12103,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12156,7 +12162,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12180,10 +12186,10 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
@@ -12194,10 +12200,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12220,13 +12226,13 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12277,7 +12283,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12304,10 +12310,10 @@
         <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>83</v>
@@ -12315,10 +12321,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12341,13 +12347,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12398,7 +12404,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12422,10 +12428,10 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12436,10 +12442,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12557,14 +12563,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12586,13 +12592,13 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12680,14 +12686,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12709,16 +12715,16 @@
         <v>137</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12767,7 +12773,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12805,10 +12811,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12831,16 +12837,16 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12866,13 +12872,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12890,7 +12896,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>92</v>
@@ -12914,24 +12920,24 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12954,13 +12960,13 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12987,13 +12993,13 @@
         <v>83</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -13011,7 +13017,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13035,24 +13041,24 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13075,13 +13081,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13132,7 +13138,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13153,13 +13159,13 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13170,14 +13176,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13196,16 +13202,16 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13255,7 +13261,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13282,7 +13288,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -13293,10 +13299,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13319,16 +13325,16 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13378,7 +13384,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13399,13 +13405,13 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3529" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3529" uniqueCount="644">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -696,16 +696,16 @@
 This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
   </si>
   <si>
+    <t>plan</t>
+  </si>
+  <si>
     <t>The kind of medication order.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
-    <t>1540: fixed value = #plan when NON-VA MEDS - ORDER NUMBER (55.05-7) case Not null</t>
-  </si>
-  <si>
-    <t>NonVAMed.NonVAMed.CPRSOrderIEN</t>
+    <t>1540: fixed value = #plan</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -827,7 +827,10 @@
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>1347: fixed value = true when NON-VA MEDS - ORDER NUMBER (55.05-7) case Not null</t>
+    <t>true</t>
+  </si>
+  <si>
+    <t>1347: fixed value = true</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
@@ -4646,7 +4649,7 @@
         <v>83</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>83</v>
@@ -4664,10 +4667,10 @@
         <v>196</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
@@ -4700,10 +4703,10 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>221</v>
@@ -5378,7 +5381,7 @@
         <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>83</v>
@@ -5432,10 +5435,10 @@
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>83</v>
@@ -5455,10 +5458,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5481,16 +5484,16 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5516,11 +5519,11 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5538,7 +5541,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5559,27 +5562,27 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5602,16 +5605,16 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5661,7 +5664,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>92</v>
@@ -5682,27 +5685,27 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5725,16 +5728,16 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5784,7 +5787,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5805,27 +5808,27 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>200</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5848,13 +5851,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5905,7 +5908,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5926,16 +5929,16 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5943,10 +5946,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5969,13 +5972,13 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6026,7 +6029,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6047,27 +6050,27 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6090,13 +6093,13 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6147,7 +6150,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6168,16 +6171,16 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6185,10 +6188,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6211,13 +6214,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6268,7 +6271,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6289,16 +6292,16 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6306,10 +6309,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6335,13 +6338,13 @@
         <v>204</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6370,10 +6373,10 @@
         <v>208</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6391,7 +6394,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6412,13 +6415,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6429,10 +6432,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6455,13 +6458,13 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6512,7 +6515,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6539,10 +6542,10 @@
         <v>83</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6550,10 +6553,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6579,13 +6582,13 @@
         <v>204</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6614,10 +6617,10 @@
         <v>208</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6635,7 +6638,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6656,27 +6659,27 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6699,16 +6702,16 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6758,7 +6761,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6779,16 +6782,16 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>200</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6796,10 +6799,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6822,13 +6825,13 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6879,7 +6882,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6900,13 +6903,13 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6917,10 +6920,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6946,10 +6949,10 @@
         <v>106</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7000,7 +7003,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7027,7 +7030,7 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7038,10 +7041,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7064,13 +7067,13 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7121,7 +7124,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7142,13 +7145,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7159,10 +7162,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7188,14 +7191,14 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7244,7 +7247,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7265,13 +7268,13 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7282,10 +7285,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7311,13 +7314,13 @@
         <v>204</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7346,10 +7349,10 @@
         <v>208</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7367,7 +7370,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7394,7 +7397,7 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7405,10 +7408,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7431,13 +7434,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7488,7 +7491,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7509,13 +7512,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7526,10 +7529,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7552,13 +7555,13 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7609,7 +7612,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7624,19 +7627,19 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7647,10 +7650,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7673,16 +7676,16 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7732,7 +7735,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7753,13 +7756,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7770,10 +7773,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7891,10 +7894,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7920,10 +7923,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>179</v>
@@ -8014,14 +8017,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8043,10 +8046,10 @@
         <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>179</v>
@@ -8101,7 +8104,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8139,10 +8142,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8165,17 +8168,17 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8224,7 +8227,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8251,21 +8254,21 @@
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8291,14 +8294,14 @@
         <v>151</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8347,7 +8350,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8374,21 +8377,21 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8414,16 +8417,16 @@
         <v>204</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8451,10 +8454,10 @@
         <v>208</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8472,7 +8475,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8499,21 +8502,21 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8539,10 +8542,10 @@
         <v>151</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8593,7 +8596,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8620,21 +8623,21 @@
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8657,19 +8660,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8718,7 +8721,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8745,7 +8748,7 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8756,10 +8759,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8782,16 +8785,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8820,10 +8823,10 @@
         <v>208</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8841,7 +8844,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8868,21 +8871,21 @@
         <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8908,16 +8911,16 @@
         <v>204</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8945,10 +8948,10 @@
         <v>208</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8966,7 +8969,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8993,21 +8996,21 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9033,14 +9036,14 @@
         <v>204</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9068,10 +9071,10 @@
         <v>208</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -9089,7 +9092,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9116,21 +9119,21 @@
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9156,16 +9159,16 @@
         <v>204</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9193,10 +9196,10 @@
         <v>208</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -9214,7 +9217,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9241,21 +9244,21 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9278,13 +9281,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9335,7 +9338,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9368,15 +9371,15 @@
         <v>83</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9494,10 +9497,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9523,10 +9526,10 @@
         <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>179</v>
@@ -9617,10 +9620,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9646,14 +9649,14 @@
         <v>204</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9681,10 +9684,10 @@
         <v>208</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9702,7 +9705,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9735,15 +9738,15 @@
         <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9766,19 +9769,19 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9827,7 +9830,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9854,21 +9857,21 @@
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9891,19 +9894,19 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9952,7 +9955,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9979,21 +9982,21 @@
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10016,19 +10019,19 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10077,7 +10080,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10104,21 +10107,21 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10141,19 +10144,19 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10202,7 +10205,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10229,7 +10232,7 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10240,10 +10243,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10266,17 +10269,17 @@
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10325,7 +10328,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10352,7 +10355,7 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10363,10 +10366,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10389,13 +10392,13 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10446,7 +10449,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10470,10 +10473,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10484,10 +10487,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10605,10 +10608,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10634,10 +10637,10 @@
         <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>179</v>
@@ -10728,14 +10731,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10757,10 +10760,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>179</v>
@@ -10815,7 +10818,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10853,10 +10856,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10879,16 +10882,16 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10938,7 +10941,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10965,7 +10968,7 @@
         <v>83</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10976,10 +10979,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11097,10 +11100,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11126,10 +11129,10 @@
         <v>137</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>179</v>
@@ -11220,14 +11223,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11249,10 +11252,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>179</v>
@@ -11307,7 +11310,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11345,10 +11348,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11371,13 +11374,13 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11428,7 +11431,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11455,7 +11458,7 @@
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -11466,10 +11469,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11492,13 +11495,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11549,7 +11552,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11576,7 +11579,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -11587,10 +11590,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11613,13 +11616,13 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11670,7 +11673,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11697,7 +11700,7 @@
         <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -11708,10 +11711,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11734,19 +11737,19 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11795,7 +11798,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11819,10 +11822,10 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>83</v>
@@ -11833,10 +11836,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11859,16 +11862,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11918,7 +11921,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11942,24 +11945,24 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11982,13 +11985,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12039,7 +12042,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12063,24 +12066,24 @@
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12103,16 +12106,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12162,7 +12165,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12186,10 +12189,10 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
@@ -12200,10 +12203,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12226,13 +12229,13 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12283,7 +12286,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12310,10 +12313,10 @@
         <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>83</v>
@@ -12321,10 +12324,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12347,13 +12350,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12404,7 +12407,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12428,10 +12431,10 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12442,10 +12445,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12563,10 +12566,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12592,10 +12595,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>179</v>
@@ -12686,14 +12689,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12715,10 +12718,10 @@
         <v>137</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>179</v>
@@ -12773,7 +12776,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12811,10 +12814,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12837,16 +12840,16 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12875,10 +12878,10 @@
         <v>208</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12896,7 +12899,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>92</v>
@@ -12920,24 +12923,24 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12963,10 +12966,10 @@
         <v>204</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12996,10 +12999,10 @@
         <v>208</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -13017,7 +13020,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13041,24 +13044,24 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13081,13 +13084,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13138,7 +13141,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13159,13 +13162,13 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13176,14 +13179,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13202,16 +13205,16 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13261,7 +13264,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13288,7 +13291,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -13299,10 +13302,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13325,16 +13328,16 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13384,7 +13387,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13405,13 +13408,13 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
     <t>MedicationRequest.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1514,7 +1514,7 @@
     <t>MedicationRequest.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6837" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6837" uniqueCount="999">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -891,6 +891,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-status</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+MedicationRequestNonVA-1737:if NULL then fixed value #active {null}MedicationRequestNonVA-1738:if NOT NULL then fixed value #inactive {null}</t>
   </si>
   <si>
     <t>1738: fixed value = #inactive when NON-VA MEDS - STATUS (55.05-5) case NOT NULL</t>
@@ -7753,25 +7757,25 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>283</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -7779,10 +7783,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7808,13 +7812,13 @@
         <v>214</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7840,13 +7844,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -7864,7 +7868,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7885,13 +7889,13 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
@@ -7902,10 +7906,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7931,13 +7935,13 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -7948,7 +7952,7 @@
         <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>83</v>
@@ -7966,10 +7970,10 @@
         <v>207</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7987,7 +7991,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>92</v>
@@ -8002,22 +8006,22 @@
         <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -8025,10 +8029,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -8054,13 +8058,13 @@
         <v>214</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -8086,13 +8090,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -8108,7 +8112,7 @@
         <v>141</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -8132,13 +8136,13 @@
         <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
@@ -8146,13 +8150,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>83</v>
@@ -8177,13 +8181,13 @@
         <v>214</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -8212,10 +8216,10 @@
         <v>207</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -8233,7 +8237,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -8257,13 +8261,13 @@
         <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -8271,10 +8275,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8300,10 +8304,10 @@
         <v>112</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8333,10 +8337,10 @@
         <v>207</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -8354,7 +8358,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -8375,16 +8379,16 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -8392,10 +8396,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8418,16 +8422,16 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8477,7 +8481,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -8504,7 +8508,7 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -8515,10 +8519,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8541,13 +8545,13 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8586,7 +8590,7 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -8596,7 +8600,7 @@
         <v>141</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -8623,7 +8627,7 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -8634,13 +8638,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -8662,13 +8666,13 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8680,7 +8684,7 @@
         <v>83</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>83</v>
@@ -8719,7 +8723,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -8734,7 +8738,7 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
@@ -8746,7 +8750,7 @@
         <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -8757,10 +8761,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8783,16 +8787,16 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8822,13 +8826,13 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -8838,7 +8842,7 @@
         <v>141</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>92</v>
@@ -8859,30 +8863,30 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>83</v>
@@ -8907,13 +8911,13 @@
         <v>214</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8943,7 +8947,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>83</v>
@@ -8961,7 +8965,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>92</v>
@@ -8976,33 +8980,33 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -9025,16 +9029,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9084,7 +9088,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>92</v>
@@ -9105,27 +9109,27 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9148,16 +9152,16 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9207,7 +9211,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -9228,27 +9232,27 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9366,10 +9370,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9489,13 +9493,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="B50" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="C50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>83</v>
@@ -9517,13 +9521,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9601,7 +9605,7 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -9612,10 +9616,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9733,10 +9737,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9854,10 +9858,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9897,7 +9901,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>83</v>
@@ -9977,10 +9981,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -10009,7 +10013,7 @@
         <v>170</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -10021,7 +10025,7 @@
         <v>83</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>83</v>
@@ -10040,7 +10044,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -10067,13 +10071,13 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
@@ -10096,10 +10100,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10125,13 +10129,13 @@
         <v>151</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -10181,7 +10185,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -10190,7 +10194,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -10219,10 +10223,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10248,13 +10252,13 @@
         <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10283,10 +10287,10 @@
         <v>219</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -10304,7 +10308,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -10342,10 +10346,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10371,13 +10375,13 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10427,7 +10431,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10454,7 +10458,7 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -10465,10 +10469,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10494,13 +10498,13 @@
         <v>151</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10550,7 +10554,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10588,10 +10592,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10614,13 +10618,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10671,7 +10675,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10692,16 +10696,16 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -10709,10 +10713,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10735,13 +10739,13 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10792,7 +10796,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10807,33 +10811,33 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10856,13 +10860,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10913,7 +10917,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10934,16 +10938,16 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10951,10 +10955,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11072,10 +11076,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11195,13 +11199,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="B64" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="C64" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>83</v>
@@ -11223,13 +11227,13 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -11307,7 +11311,7 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -11318,10 +11322,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11439,10 +11443,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11560,10 +11564,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11603,7 +11607,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>83</v>
@@ -11683,10 +11687,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11715,7 +11719,7 @@
         <v>170</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11727,7 +11731,7 @@
         <v>83</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>83</v>
@@ -11746,7 +11750,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -11773,13 +11777,13 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
@@ -11802,10 +11806,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11831,13 +11835,13 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11887,7 +11891,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11896,7 +11900,7 @@
         <v>92</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>104</v>
@@ -11925,10 +11929,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11954,13 +11958,13 @@
         <v>106</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11989,10 +11993,10 @@
         <v>219</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -12010,7 +12014,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -12048,10 +12052,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12077,13 +12081,13 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12133,7 +12137,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -12160,7 +12164,7 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -12171,10 +12175,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12200,13 +12204,13 @@
         <v>151</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12256,7 +12260,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -12294,10 +12298,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12320,13 +12324,13 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12377,7 +12381,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -12398,16 +12402,16 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>83</v>
@@ -12415,10 +12419,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12444,13 +12448,13 @@
         <v>214</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12476,13 +12480,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -12500,7 +12504,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -12521,13 +12525,13 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -12538,10 +12542,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12564,13 +12568,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12621,7 +12625,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12636,10 +12640,10 @@
         <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>83</v>
@@ -12648,10 +12652,10 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12659,10 +12663,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12688,13 +12692,13 @@
         <v>214</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12720,13 +12724,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -12744,7 +12748,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12765,27 +12769,27 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12903,10 +12907,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13026,10 +13030,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13052,19 +13056,19 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -13113,7 +13117,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -13140,21 +13144,21 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13180,16 +13184,16 @@
         <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -13238,7 +13242,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -13253,7 +13257,7 @@
         <v>104</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>83</v>
@@ -13265,21 +13269,21 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13302,16 +13306,16 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13361,7 +13365,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -13382,16 +13386,16 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>83</v>
@@ -13399,10 +13403,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13425,13 +13429,13 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13482,7 +13486,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13503,13 +13507,13 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -13520,10 +13524,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13549,10 +13553,10 @@
         <v>106</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13603,7 +13607,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13630,7 +13634,7 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -13641,10 +13645,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13667,13 +13671,13 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13724,7 +13728,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13745,13 +13749,13 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13762,10 +13766,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13791,14 +13795,14 @@
         <v>183</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -13847,7 +13851,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13868,13 +13872,13 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13885,10 +13889,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13914,13 +13918,13 @@
         <v>214</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13946,13 +13950,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -13970,7 +13974,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13997,7 +14001,7 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -14008,10 +14012,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14034,13 +14038,13 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14091,7 +14095,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -14112,13 +14116,13 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -14129,10 +14133,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14155,13 +14159,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -14212,7 +14216,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -14227,19 +14231,19 @@
         <v>104</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -14250,10 +14254,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14276,16 +14280,16 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14335,7 +14339,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14356,13 +14360,13 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -14373,10 +14377,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14494,10 +14498,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14617,14 +14621,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14646,10 +14650,10 @@
         <v>137</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>179</v>
@@ -14704,7 +14708,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14742,10 +14746,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14768,17 +14772,17 @@
         <v>93</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14827,7 +14831,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14854,21 +14858,21 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14894,14 +14898,14 @@
         <v>151</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14950,7 +14954,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14965,7 +14969,7 @@
         <v>104</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>83</v>
@@ -14977,21 +14981,21 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15017,16 +15021,16 @@
         <v>214</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -15051,13 +15055,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -15075,7 +15079,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -15102,21 +15106,21 @@
         <v>83</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15142,10 +15146,10 @@
         <v>151</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -15196,7 +15200,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -15223,21 +15227,21 @@
         <v>83</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15260,19 +15264,19 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -15321,7 +15325,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15348,7 +15352,7 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -15359,10 +15363,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15480,10 +15484,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15603,14 +15607,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -15632,10 +15636,10 @@
         <v>137</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>179</v>
@@ -15690,7 +15694,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15728,10 +15732,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15754,17 +15758,17 @@
         <v>93</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15813,7 +15817,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15840,7 +15844,7 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -15851,10 +15855,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15877,17 +15881,17 @@
         <v>93</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15936,7 +15940,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15948,7 +15952,7 @@
         <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>83</v>
@@ -15963,7 +15967,7 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -15974,10 +15978,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16095,10 +16099,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16218,10 +16222,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16244,13 +16248,13 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -16301,7 +16305,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -16328,7 +16332,7 @@
         <v>83</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
@@ -16339,10 +16343,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16365,19 +16369,19 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -16426,7 +16430,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16453,7 +16457,7 @@
         <v>83</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
@@ -16464,10 +16468,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16490,13 +16494,13 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -16547,7 +16551,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16574,7 +16578,7 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -16585,10 +16589,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16611,19 +16615,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16672,7 +16676,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16699,7 +16703,7 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
@@ -16710,10 +16714,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16736,19 +16740,19 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -16797,7 +16801,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16824,7 +16828,7 @@
         <v>83</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
@@ -16835,10 +16839,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16864,10 +16868,10 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16897,10 +16901,10 @@
         <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -16918,7 +16922,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16945,7 +16949,7 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -16956,10 +16960,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16982,13 +16986,13 @@
         <v>93</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16996,7 +17000,7 @@
         <v>83</v>
       </c>
       <c r="Q111" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="R111" t="s" s="2">
         <v>83</v>
@@ -17041,7 +17045,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -17068,7 +17072,7 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -17079,10 +17083,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17105,13 +17109,13 @@
         <v>93</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -17162,7 +17166,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -17189,7 +17193,7 @@
         <v>83</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -17200,10 +17204,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17226,13 +17230,13 @@
         <v>93</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17283,7 +17287,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -17310,7 +17314,7 @@
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
@@ -17321,10 +17325,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17347,13 +17351,13 @@
         <v>93</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17404,7 +17408,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -17431,7 +17435,7 @@
         <v>83</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -17442,10 +17446,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17471,10 +17475,10 @@
         <v>112</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17504,10 +17508,10 @@
         <v>207</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -17525,7 +17529,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -17552,7 +17556,7 @@
         <v>83</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>83</v>
@@ -17563,10 +17567,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17592,13 +17596,13 @@
         <v>112</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17628,7 +17632,7 @@
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -17646,7 +17650,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17684,10 +17688,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17710,16 +17714,16 @@
         <v>93</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -17769,7 +17773,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17807,10 +17811,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17836,16 +17840,16 @@
         <v>112</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -17873,10 +17877,10 @@
         <v>207</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>83</v>
@@ -17894,7 +17898,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17921,7 +17925,7 @@
         <v>83</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>83</v>
@@ -17932,10 +17936,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17958,13 +17962,13 @@
         <v>93</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -18015,7 +18019,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -18042,7 +18046,7 @@
         <v>83</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>83</v>
@@ -18053,10 +18057,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18082,13 +18086,13 @@
         <v>214</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -18117,10 +18121,10 @@
         <v>116</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
@@ -18138,7 +18142,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -18165,7 +18169,7 @@
         <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -18176,10 +18180,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18297,10 +18301,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18420,10 +18424,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18446,19 +18450,19 @@
         <v>93</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -18507,7 +18511,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18534,21 +18538,21 @@
         <v>83</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18574,16 +18578,16 @@
         <v>151</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -18632,7 +18636,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18647,10 +18651,10 @@
         <v>104</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>83</v>
@@ -18659,21 +18663,21 @@
         <v>83</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18696,16 +18700,16 @@
         <v>93</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -18731,13 +18735,13 @@
         <v>83</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>83</v>
@@ -18755,7 +18759,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18782,21 +18786,21 @@
         <v>83</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18822,16 +18826,16 @@
         <v>214</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18856,13 +18860,13 @@
         <v>83</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>83</v>
@@ -18880,7 +18884,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18907,21 +18911,21 @@
         <v>83</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18947,14 +18951,14 @@
         <v>214</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -18979,13 +18983,13 @@
         <v>83</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>83</v>
@@ -19003,7 +19007,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -19030,21 +19034,21 @@
         <v>83</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19162,10 +19166,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19285,10 +19289,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19311,19 +19315,19 @@
         <v>93</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -19372,7 +19376,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -19399,21 +19403,21 @@
         <v>83</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19439,16 +19443,16 @@
         <v>151</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -19497,7 +19501,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -19512,10 +19516,10 @@
         <v>104</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>83</v>
@@ -19524,21 +19528,21 @@
         <v>83</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19564,16 +19568,16 @@
         <v>214</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>83</v>
@@ -19598,13 +19602,13 @@
         <v>83</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
@@ -19622,7 +19626,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -19649,21 +19653,21 @@
         <v>83</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19686,13 +19690,13 @@
         <v>93</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19743,7 +19747,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19776,15 +19780,15 @@
         <v>83</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19902,10 +19906,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20025,10 +20029,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20054,14 +20058,14 @@
         <v>214</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
@@ -20086,13 +20090,13 @@
         <v>83</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>83</v>
@@ -20110,7 +20114,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -20143,15 +20147,15 @@
         <v>83</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20174,19 +20178,19 @@
         <v>93</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -20223,7 +20227,7 @@
         <v>83</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AC137" s="2"/>
       <c r="AD137" t="s" s="2">
@@ -20233,7 +20237,7 @@
         <v>141</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -20260,24 +20264,24 @@
         <v>83</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AP137" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>83</v>
@@ -20299,19 +20303,19 @@
         <v>83</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>83</v>
@@ -20360,7 +20364,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -20372,7 +20376,7 @@
         <v>148</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>83</v>
@@ -20387,21 +20391,21 @@
         <v>83</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20519,10 +20523,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20642,13 +20646,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="B141" t="s" s="2">
-        <v>812</v>
-      </c>
       <c r="C141" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>83</v>
@@ -20670,16 +20674,16 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20744,10 +20748,10 @@
         <v>143</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>83</v>
@@ -20767,10 +20771,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20793,19 +20797,19 @@
         <v>93</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>83</v>
@@ -20854,7 +20858,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -20881,21 +20885,21 @@
         <v>83</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AP142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20921,20 +20925,20 @@
         <v>112</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q143" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="R143" t="s" s="2">
         <v>83</v>
@@ -20958,10 +20962,10 @@
         <v>207</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>83</v>
@@ -20979,7 +20983,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -21006,21 +21010,21 @@
         <v>83</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21046,14 +21050,14 @@
         <v>151</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>83</v>
@@ -21102,7 +21106,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -21129,21 +21133,21 @@
         <v>83</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AP144" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21169,14 +21173,14 @@
         <v>106</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>83</v>
@@ -21225,7 +21229,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -21234,7 +21238,7 @@
         <v>92</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>104</v>
@@ -21252,21 +21256,21 @@
         <v>83</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AP145" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21292,16 +21296,16 @@
         <v>112</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>83</v>
@@ -21350,7 +21354,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -21377,21 +21381,21 @@
         <v>83</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AP146" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21414,19 +21418,19 @@
         <v>93</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>83</v>
@@ -21475,7 +21479,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -21502,21 +21506,21 @@
         <v>83</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21539,19 +21543,19 @@
         <v>93</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>83</v>
@@ -21600,7 +21604,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -21627,21 +21631,21 @@
         <v>83</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AP148" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21664,19 +21668,19 @@
         <v>93</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -21725,7 +21729,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -21752,7 +21756,7 @@
         <v>83</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>83</v>
@@ -21763,10 +21767,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21789,17 +21793,17 @@
         <v>93</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -21848,7 +21852,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -21875,7 +21879,7 @@
         <v>83</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>83</v>
@@ -21886,10 +21890,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21912,13 +21916,13 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -21969,7 +21973,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -21993,10 +21997,10 @@
         <v>83</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>83</v>
@@ -22007,10 +22011,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22128,10 +22132,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22251,14 +22255,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -22280,10 +22284,10 @@
         <v>137</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>179</v>
@@ -22338,7 +22342,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -22376,10 +22380,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22402,16 +22406,16 @@
         <v>83</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -22461,7 +22465,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -22488,7 +22492,7 @@
         <v>83</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AP155" t="s" s="2">
         <v>83</v>
@@ -22499,10 +22503,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22620,10 +22624,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22743,14 +22747,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -22772,10 +22776,10 @@
         <v>137</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>179</v>
@@ -22830,7 +22834,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -22868,10 +22872,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22894,13 +22898,13 @@
         <v>83</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -22951,7 +22955,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -22978,7 +22982,7 @@
         <v>83</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AP159" t="s" s="2">
         <v>83</v>
@@ -22989,10 +22993,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23015,13 +23019,13 @@
         <v>83</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -23072,7 +23076,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -23099,7 +23103,7 @@
         <v>83</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AP160" t="s" s="2">
         <v>83</v>
@@ -23110,10 +23114,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23136,13 +23140,13 @@
         <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23193,7 +23197,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -23220,7 +23224,7 @@
         <v>83</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AP161" t="s" s="2">
         <v>83</v>
@@ -23231,10 +23235,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23260,16 +23264,16 @@
         <v>249</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -23318,7 +23322,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -23342,10 +23346,10 @@
         <v>83</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>83</v>
@@ -23356,10 +23360,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23382,16 +23386,16 @@
         <v>83</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23441,7 +23445,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -23465,24 +23469,24 @@
         <v>83</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23505,13 +23509,13 @@
         <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -23562,7 +23566,7 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -23586,24 +23590,24 @@
         <v>83</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23626,16 +23630,16 @@
         <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -23685,7 +23689,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23709,10 +23713,10 @@
         <v>83</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>83</v>
@@ -23723,10 +23727,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23752,10 +23756,10 @@
         <v>257</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -23806,7 +23810,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23833,10 +23837,10 @@
         <v>83</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>83</v>
@@ -23844,10 +23848,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23870,13 +23874,13 @@
         <v>83</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -23927,7 +23931,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23951,10 +23955,10 @@
         <v>83</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AP167" t="s" s="2">
         <v>83</v>
@@ -23965,10 +23969,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24086,10 +24090,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24209,14 +24213,14 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -24238,10 +24242,10 @@
         <v>137</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>179</v>
@@ -24296,7 +24300,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -24334,10 +24338,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24360,16 +24364,16 @@
         <v>83</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24395,13 +24399,13 @@
         <v>83</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>83</v>
@@ -24419,7 +24423,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>92</v>
@@ -24443,24 +24447,24 @@
         <v>83</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24486,10 +24490,10 @@
         <v>214</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -24516,13 +24520,13 @@
         <v>83</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>83</v>
@@ -24540,7 +24544,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -24564,24 +24568,24 @@
         <v>83</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AP172" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24604,13 +24608,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -24661,7 +24665,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -24682,13 +24686,13 @@
         <v>83</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>83</v>
@@ -24699,14 +24703,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -24725,16 +24729,16 @@
         <v>83</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -24784,7 +24788,7 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -24811,7 +24815,7 @@
         <v>83</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="AP174" t="s" s="2">
         <v>83</v>
@@ -24822,10 +24826,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24848,16 +24852,16 @@
         <v>83</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -24907,7 +24911,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24928,13 +24932,13 @@
         <v>83</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="AP175" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -894,7 +894,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-MedicationRequestNonVA-1737:if NULL then fixed value #active {null}MedicationRequestNonVA-1738:if NOT NULL then fixed value #inactive {null}</t>
+mrnva-22-1737:55.05-5: if NULL then #active {null}mrnva-22-1738:55.05-5: if NOT NULL then #inactive {null}</t>
   </si>
   <si>
     <t>1738: fixed value = #inactive when NON-VA MEDS - STATUS (55.05-5) case NOT NULL</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NON-VA MEDS (55.05) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file NON-VA MEDS (55.05) to us-core-medicationrequest.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7093" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7093" uniqueCount="1018">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,7 +559,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1765: reference from NON-VA MEDS - CLINIC (55.05-13)</t>
+    <t>1765: reference based on NON-VA MEDS - CLINIC (55.05-13)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.LocationIEN</t>
@@ -777,7 +777,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1762: source value from NON-VA MEDS - ORDER NUMBER (55.05-7)</t>
+    <t>1762: source value based on NON-VA MEDS - ORDER NUMBER (55.05-7)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.CPRSOrderIEN</t>
@@ -875,7 +875,7 @@
     <t>MedicationRequest.identifier:va-ien.value</t>
   </si>
   <si>
-    <t>1763: source value from NON-VA MEDS - IEN (55.05-.001)</t>
+    <t>1763: source value based on NON-VA MEDS - IEN (55.05-.001)</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:va-ien.period</t>
@@ -903,10 +903,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mrnva-22-1737:55.05-5: if NULL then #active {null}mrnva-22-1738:55.05-5: if NOT NULL then #inactive {null}</t>
-  </si>
-  <si>
-    <t>1738: fixed value = #inactive when NON-VA MEDS - STATUS (55.05-5) case NOT NULL</t>
+mrnva-22-1737:If (55.05-5) is NULL then fixed value #active {null}mrnva-22-1738:If (55.05-5) is NOT NULL then fixed value #inactive {null}</t>
+  </si>
+  <si>
+    <t>1738: fixed value = #inactive when NON-VA MEDS - STATUS (55.05-5) if NOT NULL</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.NonVAMedStatus</t>
@@ -1175,7 +1175,11 @@
     <t>medicationCodeableConcept</t>
   </si>
   <si>
-    <t>1733: source value from NON-VA MEDS - DISPENSE DRUG (55.05-1)</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mrnva-22-1732:If 55.05-1 is null then source value from (55.05-.01) {null}</t>
+  </si>
+  <si>
+    <t>1733: source value based on NON-VA MEDS - DISPENSE DRUG (55.05-1)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.LocalDrugIEN</t>
@@ -1438,7 +1442,7 @@
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
   </si>
   <si>
-    <t>1741: source value from NON-VA MEDS - DOCUMENTED DATE (55.05-11)</t>
+    <t>1741: source value based on NON-VA MEDS - DOCUMENTED DATE (55.05-11)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.DocumentedDateTime</t>
@@ -1588,7 +1592,7 @@
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
   </si>
   <si>
-    <t>1742: reference from NON-VA MEDS - DOCUMENTED BY (55.05-12)</t>
+    <t>1742: reference based on NON-VA MEDS - DOCUMENTED BY (55.05-12)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.DocumentedByStaffIEN</t>
@@ -1688,7 +1692,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1744: source value from NON-VA MEDS - INDICATION FOR USE (55.05-15)</t>
+    <t>1744: source value based on NON-VA MEDS - INDICATION FOR USE (55.05-15)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1837,7 +1841,7 @@
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
   </si>
   <si>
-    <t>1764: source value from NON-VA MEDS - DISCLAIMER (55.05-10)</t>
+    <t>1764: source value based on NON-VA MEDS - DISCLAIMER (55.05-10)</t>
   </si>
   <si>
     <t>Medication.Statement</t>
@@ -1937,7 +1941,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>1745: source value from NON-VA MEDS - SIG (55.05-16)</t>
+    <t>1745: source value based on NON-VA MEDS - SIG (55.05-16)</t>
   </si>
   <si>
     <t>RXO-6; RXE-21</t>
@@ -2356,7 +2360,7 @@
     <t>MedicationRequest.dosageInstruction.timing.code.text</t>
   </si>
   <si>
-    <t>1736: source value from NON-VA MEDS - SCHEDULE (55.05-4)</t>
+    <t>1736: source value based on NON-VA MEDS - SCHEDULE (55.05-4)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.Schedule</t>
@@ -2465,7 +2469,7 @@
     <t>MedicationRequest.dosageInstruction.route.text</t>
   </si>
   <si>
-    <t>1735: source value from NON-VA MEDS - MEDICATION ROUTE (55.05-3)</t>
+    <t>1735: source value based on NON-VA MEDS - MEDICATION ROUTE (55.05-3)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.MedicationRoute</t>
@@ -2616,7 +2620,7 @@
 It's also possible to link to the resource narrative using the [narrativeLink extension](StructureDefinition-narrativeLink.html) which does not claim that the data is derived from the text.</t>
   </si>
   <si>
-    <t>1734: source value from NON-VA MEDS - DOSAGE (55.05-2)</t>
+    <t>1734: source value based on NON-VA MEDS - DOSAGE (55.05-2)</t>
   </si>
   <si>
     <t>NonVAMed.NonVAMed.Dosage</t>
@@ -9292,16 +9296,16 @@
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>363</v>
@@ -9321,13 +9325,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>84</v>
@@ -9349,7 +9353,7 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>359</v>
@@ -9423,7 +9427,7 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -9449,10 +9453,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9475,16 +9479,16 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9534,7 +9538,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>93</v>
@@ -9549,7 +9553,7 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>84</v>
@@ -9558,27 +9562,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9601,16 +9605,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9660,7 +9664,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9684,27 +9688,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9825,10 +9829,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9951,13 +9955,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="B52" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="C52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>84</v>
@@ -9979,13 +9983,13 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -10066,7 +10070,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -10077,10 +10081,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -10201,10 +10205,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -10325,10 +10329,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10368,7 +10372,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>84</v>
@@ -10451,10 +10455,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10483,7 +10487,7 @@
         <v>171</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -10495,7 +10499,7 @@
         <v>84</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>84</v>
@@ -10514,7 +10518,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -10541,13 +10545,13 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
@@ -10573,10 +10577,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10602,13 +10606,13 @@
         <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10658,7 +10662,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10667,7 +10671,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -10699,10 +10703,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10728,13 +10732,13 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10763,10 +10767,10 @@
         <v>221</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -10784,7 +10788,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10825,10 +10829,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10854,13 +10858,13 @@
         <v>185</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10910,7 +10914,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10940,7 +10944,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10951,10 +10955,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10980,13 +10984,13 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -11036,7 +11040,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -11077,10 +11081,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -11103,13 +11107,13 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -11160,7 +11164,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -11184,16 +11188,16 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>84</v>
@@ -11201,10 +11205,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11227,13 +11231,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -11284,7 +11288,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -11299,36 +11303,36 @@
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11351,13 +11355,13 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -11408,7 +11412,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -11432,16 +11436,16 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>84</v>
@@ -11449,10 +11453,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11573,10 +11577,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11699,13 +11703,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="B66" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="C66" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>84</v>
@@ -11727,13 +11731,13 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11814,7 +11818,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11825,10 +11829,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11949,10 +11953,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -12073,10 +12077,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -12116,7 +12120,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>84</v>
@@ -12199,10 +12203,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -12231,7 +12235,7 @@
         <v>171</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12243,7 +12247,7 @@
         <v>84</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>84</v>
@@ -12262,7 +12266,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -12289,13 +12293,13 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -12321,10 +12325,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12350,13 +12354,13 @@
         <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12406,7 +12410,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -12415,7 +12419,7 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -12447,10 +12451,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12476,13 +12480,13 @@
         <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12511,10 +12515,10 @@
         <v>221</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -12532,7 +12536,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12573,10 +12577,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12602,13 +12606,13 @@
         <v>185</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12658,7 +12662,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12688,7 +12692,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -12699,10 +12703,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12728,13 +12732,13 @@
         <v>152</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12784,7 +12788,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12825,10 +12829,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12851,13 +12855,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12908,7 +12912,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12932,16 +12936,16 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12949,10 +12953,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12978,13 +12982,13 @@
         <v>216</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -13013,10 +13017,10 @@
         <v>298</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -13034,7 +13038,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -13058,13 +13062,13 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -13075,10 +13079,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -13101,13 +13105,13 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -13158,7 +13162,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -13173,13 +13177,13 @@
         <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>84</v>
@@ -13188,10 +13192,10 @@
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>84</v>
@@ -13199,10 +13203,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13228,13 +13232,13 @@
         <v>216</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -13263,10 +13267,10 @@
         <v>298</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -13284,7 +13288,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -13308,27 +13312,27 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13449,10 +13453,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13575,10 +13579,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13601,19 +13605,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -13662,7 +13666,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13692,21 +13696,21 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13732,16 +13736,16 @@
         <v>152</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13790,7 +13794,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13805,7 +13809,7 @@
         <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>84</v>
@@ -13820,21 +13824,21 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13857,16 +13861,16 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13916,7 +13920,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13940,16 +13944,16 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>84</v>
@@ -13957,10 +13961,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13983,13 +13987,13 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -14040,7 +14044,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -14064,13 +14068,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -14081,10 +14085,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -14110,10 +14114,10 @@
         <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -14164,7 +14168,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -14194,7 +14198,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -14205,10 +14209,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14231,13 +14235,13 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -14288,7 +14292,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14312,13 +14316,13 @@
         <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14329,10 +14333,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14358,14 +14362,14 @@
         <v>185</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -14414,7 +14418,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14438,13 +14442,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14455,10 +14459,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14484,13 +14488,13 @@
         <v>216</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -14519,10 +14523,10 @@
         <v>298</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -14540,7 +14544,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14570,7 +14574,7 @@
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14581,10 +14585,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14607,13 +14611,13 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14664,7 +14668,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14688,13 +14692,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14705,10 +14709,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14731,13 +14735,13 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14788,7 +14792,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14803,22 +14807,22 @@
         <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14829,10 +14833,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14855,16 +14859,16 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -14914,7 +14918,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14938,13 +14942,13 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14955,10 +14959,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -15079,10 +15083,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -15205,14 +15209,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -15234,10 +15238,10 @@
         <v>138</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>181</v>
@@ -15292,7 +15296,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -15333,10 +15337,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15359,17 +15363,17 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15418,7 +15422,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15448,21 +15452,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15488,14 +15492,14 @@
         <v>152</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -15544,7 +15548,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15559,7 +15563,7 @@
         <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>84</v>
@@ -15574,21 +15578,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15614,16 +15618,16 @@
         <v>216</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15651,10 +15655,10 @@
         <v>298</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>84</v>
@@ -15672,7 +15676,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15702,21 +15706,21 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15742,10 +15746,10 @@
         <v>152</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -15796,7 +15800,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15826,21 +15830,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15863,19 +15867,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15924,7 +15928,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15954,7 +15958,7 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15965,10 +15969,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -16089,10 +16093,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16215,14 +16219,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16244,10 +16248,10 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>181</v>
@@ -16302,7 +16306,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -16343,10 +16347,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16369,17 +16373,17 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16428,7 +16432,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16458,7 +16462,7 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -16469,10 +16473,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16495,17 +16499,17 @@
         <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -16554,7 +16558,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -16566,7 +16570,7 @@
         <v>84</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>84</v>
@@ -16584,7 +16588,7 @@
         <v>84</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -16595,10 +16599,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16719,10 +16723,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16845,10 +16849,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16871,13 +16875,13 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -16928,7 +16932,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16958,7 +16962,7 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16969,10 +16973,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16995,19 +16999,19 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -17056,7 +17060,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -17086,7 +17090,7 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -17097,10 +17101,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17123,13 +17127,13 @@
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -17180,7 +17184,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -17210,7 +17214,7 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -17221,10 +17225,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17247,19 +17251,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -17308,7 +17312,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17338,7 +17342,7 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -17349,10 +17353,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17375,19 +17379,19 @@
         <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17436,7 +17440,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -17466,7 +17470,7 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -17477,10 +17481,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17506,10 +17510,10 @@
         <v>113</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -17539,10 +17543,10 @@
         <v>209</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -17560,7 +17564,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17590,7 +17594,7 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -17601,10 +17605,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17627,13 +17631,13 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17641,7 +17645,7 @@
         <v>84</v>
       </c>
       <c r="Q113" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="R113" t="s" s="2">
         <v>84</v>
@@ -17686,7 +17690,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17716,7 +17720,7 @@
         <v>84</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17727,10 +17731,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17753,13 +17757,13 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17810,7 +17814,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17840,7 +17844,7 @@
         <v>84</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17851,10 +17855,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17877,13 +17881,13 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17934,7 +17938,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17964,7 +17968,7 @@
         <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17975,10 +17979,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18001,13 +18005,13 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -18058,7 +18062,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -18088,7 +18092,7 @@
         <v>84</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -18099,10 +18103,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18128,10 +18132,10 @@
         <v>113</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -18161,10 +18165,10 @@
         <v>209</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -18182,7 +18186,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -18212,7 +18216,7 @@
         <v>84</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -18223,10 +18227,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18252,13 +18256,13 @@
         <v>113</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -18288,7 +18292,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>84</v>
@@ -18306,7 +18310,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -18347,10 +18351,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18373,16 +18377,16 @@
         <v>94</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -18432,7 +18436,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -18473,10 +18477,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18502,16 +18506,16 @@
         <v>113</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -18539,10 +18543,10 @@
         <v>209</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>84</v>
@@ -18560,7 +18564,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -18590,7 +18594,7 @@
         <v>84</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -18601,10 +18605,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18627,13 +18631,13 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18684,7 +18688,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18714,7 +18718,7 @@
         <v>84</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18725,10 +18729,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18754,13 +18758,13 @@
         <v>216</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -18789,10 +18793,10 @@
         <v>117</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>84</v>
@@ -18810,7 +18814,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18840,7 +18844,7 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18851,10 +18855,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18975,10 +18979,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -19101,10 +19105,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19127,19 +19131,19 @@
         <v>94</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -19188,7 +19192,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -19218,21 +19222,21 @@
         <v>84</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19258,16 +19262,16 @@
         <v>152</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19316,7 +19320,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19331,13 +19335,13 @@
         <v>105</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
@@ -19346,21 +19350,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19383,16 +19387,16 @@
         <v>94</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -19421,10 +19425,10 @@
         <v>298</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -19442,7 +19446,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19472,21 +19476,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19512,16 +19516,16 @@
         <v>216</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19549,10 +19553,10 @@
         <v>298</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>84</v>
@@ -19570,7 +19574,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19600,21 +19604,21 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19640,14 +19644,14 @@
         <v>216</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19675,10 +19679,10 @@
         <v>298</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>84</v>
@@ -19696,7 +19700,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19726,21 +19730,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19861,10 +19865,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19987,10 +19991,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -20013,19 +20017,19 @@
         <v>94</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -20074,7 +20078,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -20104,21 +20108,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20144,16 +20148,16 @@
         <v>152</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -20202,7 +20206,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20217,13 +20221,13 @@
         <v>105</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>84</v>
@@ -20232,21 +20236,21 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20272,16 +20276,16 @@
         <v>216</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20309,10 +20313,10 @@
         <v>298</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>84</v>
@@ -20330,7 +20334,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20360,21 +20364,21 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20397,13 +20401,13 @@
         <v>94</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -20454,7 +20458,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20490,15 +20494,15 @@
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20619,10 +20623,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20745,10 +20749,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20774,14 +20778,14 @@
         <v>216</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20809,10 +20813,10 @@
         <v>298</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>84</v>
@@ -20830,7 +20834,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20866,15 +20870,15 @@
         <v>84</v>
       </c>
       <c r="AR138" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20897,19 +20901,19 @@
         <v>94</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>84</v>
@@ -20956,7 +20960,7 @@
         <v>142</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20986,24 +20990,24 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR139" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>84</v>
@@ -21025,19 +21029,19 @@
         <v>94</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>84</v>
@@ -21086,7 +21090,7 @@
         <v>84</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>82</v>
@@ -21116,21 +21120,21 @@
         <v>84</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21251,10 +21255,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21377,13 +21381,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="B143" t="s" s="2">
-        <v>830</v>
-      </c>
       <c r="C143" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>84</v>
@@ -21405,16 +21409,16 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -21479,13 +21483,13 @@
         <v>144</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>84</v>
@@ -21505,10 +21509,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21531,19 +21535,19 @@
         <v>94</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>84</v>
@@ -21592,7 +21596,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21622,21 +21626,21 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21662,20 +21666,20 @@
         <v>113</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q145" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="R145" t="s" s="2">
         <v>84</v>
@@ -21699,10 +21703,10 @@
         <v>209</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>84</v>
@@ -21720,7 +21724,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21750,21 +21754,21 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR145" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21790,14 +21794,14 @@
         <v>152</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21846,7 +21850,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21876,21 +21880,21 @@
         <v>84</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR146" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21916,14 +21920,14 @@
         <v>107</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>84</v>
@@ -21972,7 +21976,7 @@
         <v>84</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>82</v>
@@ -21981,7 +21985,7 @@
         <v>93</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>105</v>
@@ -22002,21 +22006,21 @@
         <v>84</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AQ147" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22042,16 +22046,16 @@
         <v>113</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>84</v>
@@ -22100,7 +22104,7 @@
         <v>84</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>82</v>
@@ -22130,21 +22134,21 @@
         <v>84</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AQ148" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22167,19 +22171,19 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>84</v>
@@ -22228,7 +22232,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -22258,21 +22262,21 @@
         <v>84</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22295,19 +22299,19 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>84</v>
@@ -22356,7 +22360,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22386,21 +22390,21 @@
         <v>84</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22423,19 +22427,19 @@
         <v>94</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>84</v>
@@ -22484,7 +22488,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22514,7 +22518,7 @@
         <v>84</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
@@ -22525,10 +22529,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22551,17 +22555,17 @@
         <v>94</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>84</v>
@@ -22610,7 +22614,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22640,7 +22644,7 @@
         <v>84</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
@@ -22651,10 +22655,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22677,13 +22681,13 @@
         <v>84</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22734,7 +22738,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22761,10 +22765,10 @@
         <v>84</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
@@ -22775,10 +22779,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22899,10 +22903,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23025,14 +23029,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -23054,10 +23058,10 @@
         <v>138</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>181</v>
@@ -23112,7 +23116,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -23153,10 +23157,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23179,16 +23183,16 @@
         <v>84</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -23238,7 +23242,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -23268,7 +23272,7 @@
         <v>84</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
@@ -23279,10 +23283,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23403,10 +23407,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23529,14 +23533,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -23558,10 +23562,10 @@
         <v>138</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>181</v>
@@ -23616,7 +23620,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23657,10 +23661,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23683,13 +23687,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23740,7 +23744,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23770,7 +23774,7 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>84</v>
@@ -23781,10 +23785,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23807,13 +23811,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23864,7 +23868,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23894,7 +23898,7 @@
         <v>84</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23905,10 +23909,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23931,13 +23935,13 @@
         <v>84</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23988,7 +23992,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -24018,7 +24022,7 @@
         <v>84</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>84</v>
@@ -24029,10 +24033,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24058,16 +24062,16 @@
         <v>252</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>84</v>
@@ -24116,7 +24120,7 @@
         <v>84</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -24143,10 +24147,10 @@
         <v>84</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>84</v>
@@ -24157,10 +24161,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24183,16 +24187,16 @@
         <v>84</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -24242,7 +24246,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24269,24 +24273,24 @@
         <v>84</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR165" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24309,13 +24313,13 @@
         <v>84</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24366,7 +24370,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>82</v>
@@ -24393,24 +24397,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24433,16 +24437,16 @@
         <v>84</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24492,7 +24496,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24519,10 +24523,10 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
@@ -24533,10 +24537,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24562,10 +24566,10 @@
         <v>260</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24616,7 +24620,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24646,10 +24650,10 @@
         <v>84</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>84</v>
@@ -24657,10 +24661,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24683,13 +24687,13 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -24740,7 +24744,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24767,10 +24771,10 @@
         <v>84</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24781,10 +24785,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24905,10 +24909,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25031,14 +25035,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -25060,10 +25064,10 @@
         <v>138</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N172" t="s" s="2">
         <v>181</v>
@@ -25118,7 +25122,7 @@
         <v>84</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>82</v>
@@ -25159,10 +25163,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25185,16 +25189,16 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -25223,10 +25227,10 @@
         <v>298</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>84</v>
@@ -25244,7 +25248,7 @@
         <v>84</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>93</v>
@@ -25271,24 +25275,24 @@
         <v>84</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AP173" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="AQ173" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR173" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25314,10 +25318,10 @@
         <v>216</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -25347,10 +25351,10 @@
         <v>298</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>84</v>
@@ -25368,7 +25372,7 @@
         <v>84</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>82</v>
@@ -25395,24 +25399,24 @@
         <v>84</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="AP174" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="AQ174" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR174" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25435,13 +25439,13 @@
         <v>84</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -25492,7 +25496,7 @@
         <v>84</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>82</v>
@@ -25516,13 +25520,13 @@
         <v>84</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="AP175" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="AQ175" t="s" s="2">
         <v>84</v>
@@ -25533,14 +25537,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -25559,16 +25563,16 @@
         <v>84</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -25618,7 +25622,7 @@
         <v>84</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>82</v>
@@ -25648,7 +25652,7 @@
         <v>84</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AQ176" t="s" s="2">
         <v>84</v>
@@ -25659,10 +25663,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25685,16 +25689,16 @@
         <v>84</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -25744,7 +25748,7 @@
         <v>84</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>82</v>
@@ -25768,13 +25772,13 @@
         <v>84</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP177" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="AQ177" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7093" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7093" uniqueCount="1020">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -705,6 +705,14 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="FILL"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -715,6 +723,9 @@
   </si>
   <si>
     <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>1762-2: fixed value = http://terminology.hl7.org/CodeSystem/v2-0203#FILL</t>
   </si>
   <si>
     <t>CX.5</t>
@@ -6070,7 +6081,7 @@
         <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>84</v>
@@ -6101,7 +6112,7 @@
         <v>84</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>84</v>
@@ -6116,13 +6127,13 @@
         <v>84</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>84</v>
@@ -6140,7 +6151,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -6155,7 +6166,7 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
@@ -6176,15 +6187,15 @@
         <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -6210,16 +6221,16 @@
         <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -6229,10 +6240,10 @@
         <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>84</v>
@@ -6268,7 +6279,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -6283,7 +6294,7 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
@@ -6298,21 +6309,21 @@
         <v>84</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -6338,13 +6349,13 @@
         <v>152</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -6358,7 +6369,7 @@
         <v>84</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>84</v>
@@ -6394,7 +6405,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -6409,13 +6420,13 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
@@ -6424,21 +6435,21 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -6461,13 +6472,13 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -6518,7 +6529,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -6548,21 +6559,21 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6585,16 +6596,16 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -6644,7 +6655,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -6674,24 +6685,24 @@
         <v>84</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>184</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>84</v>
@@ -6813,7 +6824,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>198</v>
@@ -6937,7 +6948,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>200</v>
@@ -7063,7 +7074,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>204</v>
@@ -7191,7 +7202,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>215</v>
@@ -7254,13 +7265,13 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
@@ -7278,7 +7289,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -7314,15 +7325,15 @@
         <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -7348,16 +7359,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -7367,10 +7378,10 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>84</v>
@@ -7406,7 +7417,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -7421,7 +7432,7 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -7436,21 +7447,21 @@
         <v>84</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -7476,13 +7487,13 @@
         <v>152</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -7496,7 +7507,7 @@
         <v>84</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>84</v>
@@ -7532,7 +7543,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -7547,7 +7558,7 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
@@ -7562,21 +7573,21 @@
         <v>84</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7599,13 +7610,13 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -7656,7 +7667,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -7686,21 +7697,21 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7723,16 +7734,16 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7782,7 +7793,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7812,21 +7823,21 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7852,13 +7863,13 @@
         <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -7887,10 +7898,10 @@
         <v>209</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -7908,7 +7919,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>93</v>
@@ -7920,28 +7931,28 @@
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -7949,10 +7960,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7978,13 +7989,13 @@
         <v>216</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -8010,13 +8021,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -8034,7 +8045,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -8058,13 +8069,13 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -8075,10 +8086,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -8104,13 +8115,13 @@
         <v>113</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -8121,7 +8132,7 @@
         <v>84</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>84</v>
@@ -8139,10 +8150,10 @@
         <v>209</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -8160,7 +8171,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>93</v>
@@ -8175,7 +8186,7 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
@@ -8184,16 +8195,16 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -8201,10 +8212,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -8230,13 +8241,13 @@
         <v>216</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -8262,19 +8273,19 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
@@ -8284,7 +8295,7 @@
         <v>142</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -8299,7 +8310,7 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>84</v>
@@ -8311,13 +8322,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -8325,13 +8336,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>84</v>
@@ -8356,13 +8367,13 @@
         <v>216</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -8391,10 +8402,10 @@
         <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -8412,7 +8423,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -8427,7 +8438,7 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
@@ -8439,13 +8450,13 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -8453,10 +8464,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8482,10 +8493,10 @@
         <v>113</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8515,10 +8526,10 @@
         <v>209</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -8536,7 +8547,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -8560,16 +8571,16 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -8577,10 +8588,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8603,16 +8614,16 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8662,7 +8673,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8692,7 +8703,7 @@
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -8703,10 +8714,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8729,13 +8740,13 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8774,17 +8785,17 @@
         <v>84</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8814,7 +8825,7 @@
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8825,13 +8836,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>84</v>
@@ -8853,13 +8864,13 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8871,7 +8882,7 @@
         <v>84</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>84</v>
@@ -8910,7 +8921,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8925,7 +8936,7 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
@@ -8940,7 +8951,7 @@
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8951,13 +8962,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>84</v>
@@ -8979,13 +8990,13 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -9036,7 +9047,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -9051,7 +9062,7 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -9066,7 +9077,7 @@
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -9077,10 +9088,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -9103,16 +9114,16 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -9138,27 +9149,27 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>93</v>
@@ -9182,30 +9193,30 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -9230,13 +9241,13 @@
         <v>216</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9262,11 +9273,11 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -9284,7 +9295,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>93</v>
@@ -9296,42 +9307,42 @@
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>84</v>
@@ -9353,16 +9364,16 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9412,7 +9423,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>93</v>
@@ -9427,7 +9438,7 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -9436,27 +9447,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9479,16 +9490,16 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9538,7 +9549,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>93</v>
@@ -9553,7 +9564,7 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>84</v>
@@ -9562,27 +9573,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9605,16 +9616,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9664,7 +9675,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9688,27 +9699,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9829,10 +9840,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9955,13 +9966,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>84</v>
@@ -9983,13 +9994,13 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -10070,7 +10081,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -10081,10 +10092,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -10205,10 +10216,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -10329,10 +10340,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10372,7 +10383,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>84</v>
@@ -10455,10 +10466,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10487,7 +10498,7 @@
         <v>171</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -10499,7 +10510,7 @@
         <v>84</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>84</v>
@@ -10518,7 +10529,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -10545,13 +10556,13 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
@@ -10577,10 +10588,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10606,13 +10617,13 @@
         <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10662,7 +10673,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10671,7 +10682,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -10703,10 +10714,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10732,13 +10743,13 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10764,13 +10775,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -10788,7 +10799,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10829,10 +10840,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10858,13 +10869,13 @@
         <v>185</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10914,7 +10925,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10944,7 +10955,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10955,10 +10966,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10984,13 +10995,13 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -11040,7 +11051,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -11081,10 +11092,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -11107,13 +11118,13 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -11164,7 +11175,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -11188,16 +11199,16 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>84</v>
@@ -11205,10 +11216,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11231,13 +11242,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -11288,7 +11299,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -11303,36 +11314,36 @@
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11355,13 +11366,13 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -11412,7 +11423,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -11436,16 +11447,16 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>84</v>
@@ -11453,10 +11464,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11577,10 +11588,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11703,13 +11714,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>84</v>
@@ -11731,13 +11742,13 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11818,7 +11829,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11829,10 +11840,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11953,10 +11964,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -12077,10 +12088,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -12120,7 +12131,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>84</v>
@@ -12203,10 +12214,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -12235,7 +12246,7 @@
         <v>171</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12247,7 +12258,7 @@
         <v>84</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>84</v>
@@ -12266,7 +12277,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -12293,13 +12304,13 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -12325,10 +12336,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12354,13 +12365,13 @@
         <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12410,7 +12421,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -12419,7 +12430,7 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -12451,10 +12462,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12480,13 +12491,13 @@
         <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12512,13 +12523,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -12536,7 +12547,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12577,10 +12588,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12606,13 +12617,13 @@
         <v>185</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12662,7 +12673,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12692,7 +12703,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -12703,10 +12714,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12732,13 +12743,13 @@
         <v>152</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12788,7 +12799,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12829,10 +12840,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12855,13 +12866,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12912,7 +12923,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12936,16 +12947,16 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12953,10 +12964,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12982,13 +12993,13 @@
         <v>216</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -13014,13 +13025,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -13038,7 +13049,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -13062,13 +13073,13 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -13079,10 +13090,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -13105,13 +13116,13 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -13162,7 +13173,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -13177,13 +13188,13 @@
         <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>84</v>
@@ -13192,10 +13203,10 @@
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>84</v>
@@ -13203,10 +13214,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13232,13 +13243,13 @@
         <v>216</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -13264,13 +13275,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -13288,7 +13299,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -13312,27 +13323,27 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13453,10 +13464,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13579,10 +13590,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13605,19 +13616,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -13666,7 +13677,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13696,21 +13707,21 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13736,16 +13747,16 @@
         <v>152</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13794,7 +13805,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13809,7 +13820,7 @@
         <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>84</v>
@@ -13824,21 +13835,21 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13861,16 +13872,16 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13920,7 +13931,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13944,16 +13955,16 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>84</v>
@@ -13961,10 +13972,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13987,13 +13998,13 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -14044,7 +14055,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -14068,13 +14079,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -14085,10 +14096,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -14114,10 +14125,10 @@
         <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -14168,7 +14179,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -14198,7 +14209,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -14209,10 +14220,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14235,13 +14246,13 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -14292,7 +14303,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14316,13 +14327,13 @@
         <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14333,10 +14344,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14362,14 +14373,14 @@
         <v>185</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -14418,7 +14429,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14442,13 +14453,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14459,10 +14470,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14488,13 +14499,13 @@
         <v>216</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -14520,13 +14531,13 @@
         <v>84</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -14544,7 +14555,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14574,7 +14585,7 @@
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14585,10 +14596,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14611,13 +14622,13 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14668,7 +14679,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14692,13 +14703,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14709,10 +14720,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14735,13 +14746,13 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14792,7 +14803,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14807,22 +14818,22 @@
         <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14833,10 +14844,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14859,16 +14870,16 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -14918,7 +14929,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14942,13 +14953,13 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14959,10 +14970,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -15083,10 +15094,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -15209,14 +15220,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -15238,10 +15249,10 @@
         <v>138</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>181</v>
@@ -15296,7 +15307,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -15337,10 +15348,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15363,17 +15374,17 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15422,7 +15433,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15452,21 +15463,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15492,14 +15503,14 @@
         <v>152</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -15548,7 +15559,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15563,7 +15574,7 @@
         <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>84</v>
@@ -15578,21 +15589,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15618,16 +15629,16 @@
         <v>216</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15652,13 +15663,13 @@
         <v>84</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>84</v>
@@ -15676,7 +15687,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15706,21 +15717,21 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15746,10 +15757,10 @@
         <v>152</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -15800,7 +15811,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15830,21 +15841,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15867,19 +15878,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15928,7 +15939,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15958,7 +15969,7 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15969,10 +15980,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -16093,10 +16104,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16219,14 +16230,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16248,10 +16259,10 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>181</v>
@@ -16306,7 +16317,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -16347,10 +16358,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16373,17 +16384,17 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16432,7 +16443,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16462,7 +16473,7 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -16473,10 +16484,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16499,17 +16510,17 @@
         <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -16558,7 +16569,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -16570,7 +16581,7 @@
         <v>84</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>84</v>
@@ -16588,7 +16599,7 @@
         <v>84</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -16599,10 +16610,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16723,10 +16734,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16849,10 +16860,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16875,13 +16886,13 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -16932,7 +16943,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16962,7 +16973,7 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16973,10 +16984,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16999,19 +17010,19 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -17060,7 +17071,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -17090,7 +17101,7 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -17101,10 +17112,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17127,13 +17138,13 @@
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -17184,7 +17195,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -17214,7 +17225,7 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -17225,10 +17236,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17251,19 +17262,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -17312,7 +17323,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17342,7 +17353,7 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -17353,10 +17364,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17379,19 +17390,19 @@
         <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17440,7 +17451,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -17470,7 +17481,7 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -17481,10 +17492,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17510,10 +17521,10 @@
         <v>113</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -17543,10 +17554,10 @@
         <v>209</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -17564,7 +17575,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17594,7 +17605,7 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -17605,10 +17616,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17631,13 +17642,13 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17645,7 +17656,7 @@
         <v>84</v>
       </c>
       <c r="Q113" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="R113" t="s" s="2">
         <v>84</v>
@@ -17690,7 +17701,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17720,7 +17731,7 @@
         <v>84</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17731,10 +17742,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17757,13 +17768,13 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17814,7 +17825,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17844,7 +17855,7 @@
         <v>84</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17855,10 +17866,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17881,13 +17892,13 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17938,7 +17949,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17968,7 +17979,7 @@
         <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17979,10 +17990,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18005,13 +18016,13 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -18062,7 +18073,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -18092,7 +18103,7 @@
         <v>84</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -18103,10 +18114,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18132,10 +18143,10 @@
         <v>113</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -18165,10 +18176,10 @@
         <v>209</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -18186,7 +18197,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -18216,7 +18227,7 @@
         <v>84</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -18227,10 +18238,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18256,13 +18267,13 @@
         <v>113</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -18292,7 +18303,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>84</v>
@@ -18310,7 +18321,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -18351,10 +18362,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18377,16 +18388,16 @@
         <v>94</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -18436,7 +18447,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -18477,10 +18488,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18506,16 +18517,16 @@
         <v>113</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -18543,10 +18554,10 @@
         <v>209</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>84</v>
@@ -18564,7 +18575,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -18594,7 +18605,7 @@
         <v>84</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -18605,10 +18616,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18631,13 +18642,13 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18688,7 +18699,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18718,7 +18729,7 @@
         <v>84</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18729,10 +18740,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18758,13 +18769,13 @@
         <v>216</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -18793,10 +18804,10 @@
         <v>117</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>84</v>
@@ -18814,7 +18825,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18844,7 +18855,7 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18855,10 +18866,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18979,10 +18990,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -19105,10 +19116,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19131,19 +19142,19 @@
         <v>94</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -19192,7 +19203,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -19222,21 +19233,21 @@
         <v>84</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19262,16 +19273,16 @@
         <v>152</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19320,7 +19331,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19335,13 +19346,13 @@
         <v>105</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
@@ -19350,21 +19361,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19387,16 +19398,16 @@
         <v>94</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -19422,13 +19433,13 @@
         <v>84</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -19446,7 +19457,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19476,21 +19487,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19516,16 +19527,16 @@
         <v>216</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19550,13 +19561,13 @@
         <v>84</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>84</v>
@@ -19574,7 +19585,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19604,21 +19615,21 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19644,14 +19655,14 @@
         <v>216</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19676,13 +19687,13 @@
         <v>84</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>84</v>
@@ -19700,7 +19711,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19730,21 +19741,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19865,10 +19876,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19991,10 +20002,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -20017,19 +20028,19 @@
         <v>94</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -20078,7 +20089,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -20108,21 +20119,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20148,16 +20159,16 @@
         <v>152</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -20206,7 +20217,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20221,13 +20232,13 @@
         <v>105</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>84</v>
@@ -20236,21 +20247,21 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20276,16 +20287,16 @@
         <v>216</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20310,13 +20321,13 @@
         <v>84</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>84</v>
@@ -20334,7 +20345,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20364,21 +20375,21 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20401,13 +20412,13 @@
         <v>94</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -20458,7 +20469,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20494,15 +20505,15 @@
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20623,10 +20634,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20749,10 +20760,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20778,14 +20789,14 @@
         <v>216</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20810,13 +20821,13 @@
         <v>84</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>84</v>
@@ -20834,7 +20845,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20870,15 +20881,15 @@
         <v>84</v>
       </c>
       <c r="AR138" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20901,19 +20912,19 @@
         <v>94</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>84</v>
@@ -20950,7 +20961,7 @@
         <v>84</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
@@ -20960,7 +20971,7 @@
         <v>142</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20990,24 +21001,24 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR139" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>84</v>
@@ -21029,19 +21040,19 @@
         <v>94</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>84</v>
@@ -21090,7 +21101,7 @@
         <v>84</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>82</v>
@@ -21120,21 +21131,21 @@
         <v>84</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21255,10 +21266,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21381,13 +21392,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>84</v>
@@ -21409,16 +21420,16 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -21483,13 +21494,13 @@
         <v>144</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>84</v>
@@ -21509,10 +21520,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21535,19 +21546,19 @@
         <v>94</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>84</v>
@@ -21596,7 +21607,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21626,21 +21637,21 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21666,20 +21677,20 @@
         <v>113</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q145" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="R145" t="s" s="2">
         <v>84</v>
@@ -21703,10 +21714,10 @@
         <v>209</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>84</v>
@@ -21724,7 +21735,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21754,21 +21765,21 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR145" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21794,14 +21805,14 @@
         <v>152</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21850,7 +21861,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21880,21 +21891,21 @@
         <v>84</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR146" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21920,14 +21931,14 @@
         <v>107</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>84</v>
@@ -21976,7 +21987,7 @@
         <v>84</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>82</v>
@@ -21985,7 +21996,7 @@
         <v>93</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>105</v>
@@ -22006,21 +22017,21 @@
         <v>84</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="AQ147" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22046,16 +22057,16 @@
         <v>113</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>84</v>
@@ -22104,7 +22115,7 @@
         <v>84</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>82</v>
@@ -22134,21 +22145,21 @@
         <v>84</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="AQ148" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22171,19 +22182,19 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>84</v>
@@ -22232,7 +22243,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -22262,21 +22273,21 @@
         <v>84</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22299,19 +22310,19 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>84</v>
@@ -22360,7 +22371,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22390,21 +22401,21 @@
         <v>84</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22427,19 +22438,19 @@
         <v>94</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>84</v>
@@ -22488,7 +22499,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22518,7 +22529,7 @@
         <v>84</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
@@ -22529,10 +22540,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22555,17 +22566,17 @@
         <v>94</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>84</v>
@@ -22614,7 +22625,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22644,7 +22655,7 @@
         <v>84</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
@@ -22655,10 +22666,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22681,13 +22692,13 @@
         <v>84</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22738,7 +22749,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22765,10 +22776,10 @@
         <v>84</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
@@ -22779,10 +22790,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22903,10 +22914,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23029,14 +23040,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -23058,10 +23069,10 @@
         <v>138</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>181</v>
@@ -23116,7 +23127,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -23157,10 +23168,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23183,16 +23194,16 @@
         <v>84</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -23242,7 +23253,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -23272,7 +23283,7 @@
         <v>84</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
@@ -23283,10 +23294,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23407,10 +23418,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23533,14 +23544,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -23562,10 +23573,10 @@
         <v>138</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>181</v>
@@ -23620,7 +23631,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23661,10 +23672,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23687,13 +23698,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23744,7 +23755,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23774,7 +23785,7 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>84</v>
@@ -23785,10 +23796,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23811,13 +23822,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23868,7 +23879,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23898,7 +23909,7 @@
         <v>84</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23909,10 +23920,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23935,13 +23946,13 @@
         <v>84</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23992,7 +24003,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -24022,7 +24033,7 @@
         <v>84</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>84</v>
@@ -24033,10 +24044,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24059,19 +24070,19 @@
         <v>84</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>84</v>
@@ -24120,7 +24131,7 @@
         <v>84</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -24147,10 +24158,10 @@
         <v>84</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>84</v>
@@ -24161,10 +24172,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24187,16 +24198,16 @@
         <v>84</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -24246,7 +24257,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24273,24 +24284,24 @@
         <v>84</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR165" t="s" s="2">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24313,13 +24324,13 @@
         <v>84</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24370,7 +24381,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>82</v>
@@ -24397,24 +24408,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24437,16 +24448,16 @@
         <v>84</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24496,7 +24507,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24523,10 +24534,10 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
@@ -24537,10 +24548,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24563,13 +24574,13 @@
         <v>84</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24620,7 +24631,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24650,10 +24661,10 @@
         <v>84</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>84</v>
@@ -24661,10 +24672,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24687,13 +24698,13 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -24744,7 +24755,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24771,10 +24782,10 @@
         <v>84</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24785,10 +24796,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24909,10 +24920,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25035,14 +25046,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -25064,10 +25075,10 @@
         <v>138</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N172" t="s" s="2">
         <v>181</v>
@@ -25122,7 +25133,7 @@
         <v>84</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>82</v>
@@ -25163,10 +25174,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25189,16 +25200,16 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -25224,13 +25235,13 @@
         <v>84</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>84</v>
@@ -25248,7 +25259,7 @@
         <v>84</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>93</v>
@@ -25275,24 +25286,24 @@
         <v>84</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="AP173" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="AQ173" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR173" t="s" s="2">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25318,10 +25329,10 @@
         <v>216</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -25348,13 +25359,13 @@
         <v>84</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>84</v>
@@ -25372,7 +25383,7 @@
         <v>84</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>82</v>
@@ -25399,24 +25410,24 @@
         <v>84</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="AP174" t="s" s="2">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="AQ174" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR174" t="s" s="2">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25439,13 +25450,13 @@
         <v>84</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -25496,7 +25507,7 @@
         <v>84</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>82</v>
@@ -25520,13 +25531,13 @@
         <v>84</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="AP175" t="s" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="AQ175" t="s" s="2">
         <v>84</v>
@@ -25537,14 +25548,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -25563,16 +25574,16 @@
         <v>84</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -25622,7 +25633,7 @@
         <v>84</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>82</v>
@@ -25652,7 +25663,7 @@
         <v>84</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="AQ176" t="s" s="2">
         <v>84</v>
@@ -25663,10 +25674,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25689,16 +25700,16 @@
         <v>84</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -25748,7 +25759,7 @@
         <v>84</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>82</v>
@@ -25772,13 +25783,13 @@
         <v>84</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP177" t="s" s="2">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="AQ177" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -914,7 +914,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mrnva-22-1737:If (55.05-5) is NULL then fixed value #active {null}mrnva-22-1738:If (55.05-5) is NOT NULL then fixed value #inactive {null}</t>
+mrnva-22-1737:If (55.05-5) is NULL then fixed value #active {true}mrnva-22-1738:If (55.05-5) is NOT NULL then fixed value #inactive {true}</t>
   </si>
   <si>
     <t>1738: fixed value = #inactive when NON-VA MEDS - STATUS (55.05-5) if NOT NULL</t>
@@ -1187,7 +1187,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mrnva-22-1732:If 55.05-1 is null then source value from (55.05-.01) {null}</t>
+mrnva-22-1732:If 55.05-1 is null then source value from (55.05-.01) {true}</t>
   </si>
   <si>
     <t>1733: source value based on NON-VA MEDS - DISPENSE DRUG (55.05-1)</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7093" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7093" uniqueCount="1019">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1022,9 +1022,6 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>2177: target not supported</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -8310,22 +8307,22 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>315</v>
@@ -8336,13 +8333,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>316</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>84</v>
@@ -8402,7 +8399,7 @@
         <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>321</v>
@@ -8438,7 +8435,7 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
@@ -8450,10 +8447,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>315</v>
@@ -8464,10 +8461,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8493,10 +8490,10 @@
         <v>113</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8526,11 +8523,11 @@
         <v>209</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
@@ -8547,7 +8544,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -8571,16 +8568,16 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -8588,10 +8585,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8614,16 +8611,16 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8673,7 +8670,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8703,7 +8700,7 @@
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -8714,10 +8711,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8740,13 +8737,13 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8785,17 +8782,17 @@
         <v>84</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8825,7 +8822,7 @@
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8836,13 +8833,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>84</v>
@@ -8864,13 +8861,13 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8882,7 +8879,7 @@
         <v>84</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>84</v>
@@ -8921,7 +8918,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8936,7 +8933,7 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
@@ -8951,7 +8948,7 @@
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8962,13 +8959,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>84</v>
@@ -8990,13 +8987,13 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -9047,7 +9044,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -9062,7 +9059,7 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -9077,7 +9074,7 @@
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -9088,10 +9085,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -9114,16 +9111,16 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -9153,23 +9150,23 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>93</v>
@@ -9193,30 +9190,30 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AP45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AQ45" t="s" s="2">
+      <c r="AR45" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -9241,13 +9238,13 @@
         <v>216</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9277,72 +9274,72 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AA46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AQ46" t="s" s="2">
+      <c r="AR46" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>84</v>
@@ -9364,16 +9361,16 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9423,7 +9420,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>93</v>
@@ -9438,7 +9435,7 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -9447,27 +9444,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AQ47" t="s" s="2">
+      <c r="AR47" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9490,16 +9487,16 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9549,7 +9546,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>93</v>
@@ -9564,36 +9561,36 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AQ48" t="s" s="2">
+      <c r="AR48" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>390</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9616,16 +9613,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9675,7 +9672,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9699,27 +9696,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>293</v>
       </c>
       <c r="AP49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AQ49" t="s" s="2">
+      <c r="AR49" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9840,10 +9837,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9966,13 +9963,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>84</v>
@@ -9994,13 +9991,13 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -10081,7 +10078,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -10092,10 +10089,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -10216,10 +10213,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -10340,10 +10337,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10383,7 +10380,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>84</v>
@@ -10466,10 +10463,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10498,7 +10495,7 @@
         <v>171</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -10510,7 +10507,7 @@
         <v>84</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>84</v>
@@ -10529,7 +10526,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -10556,13 +10553,13 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
@@ -10588,10 +10585,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10617,13 +10614,13 @@
         <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10673,16 +10670,16 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI57" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -10714,10 +10711,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10743,13 +10740,13 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10778,28 +10775,28 @@
         <v>222</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="Z58" t="s" s="2">
+      <c r="AA58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10840,10 +10837,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10869,13 +10866,13 @@
         <v>185</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10925,7 +10922,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10955,7 +10952,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10966,10 +10963,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10995,13 +10992,13 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -11051,7 +11048,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -11092,10 +11089,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -11118,13 +11115,13 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -11175,7 +11172,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -11199,16 +11196,16 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="AQ61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>84</v>
@@ -11216,10 +11213,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11242,13 +11239,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -11299,7 +11296,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -11314,36 +11311,36 @@
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AP62" t="s" s="2">
+      <c r="AQ62" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AQ62" t="s" s="2">
+      <c r="AR62" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>463</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11366,13 +11363,13 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -11423,7 +11420,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -11447,16 +11444,16 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>84</v>
@@ -11464,10 +11461,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11588,10 +11585,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11714,13 +11711,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>84</v>
@@ -11742,13 +11739,13 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11829,7 +11826,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11840,10 +11837,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11964,10 +11961,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -12088,10 +12085,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -12131,7 +12128,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>84</v>
@@ -12214,10 +12211,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -12246,7 +12243,7 @@
         <v>171</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12258,7 +12255,7 @@
         <v>84</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>84</v>
@@ -12277,7 +12274,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -12304,13 +12301,13 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -12336,10 +12333,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12365,13 +12362,13 @@
         <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12421,16 +12418,16 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -12462,10 +12459,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12491,13 +12488,13 @@
         <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12526,28 +12523,28 @@
         <v>222</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12588,10 +12585,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12617,13 +12614,13 @@
         <v>185</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12673,7 +12670,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12703,7 +12700,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -12714,10 +12711,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12743,13 +12740,13 @@
         <v>152</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12799,7 +12796,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12840,10 +12837,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12866,13 +12863,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12923,7 +12920,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12947,16 +12944,16 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12964,10 +12961,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12993,13 +12990,13 @@
         <v>216</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -13028,11 +13025,11 @@
         <v>300</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
       </c>
@@ -13049,7 +13046,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -13073,13 +13070,13 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -13090,10 +13087,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -13116,13 +13113,13 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -13173,7 +13170,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -13188,25 +13185,25 @@
         <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AL77" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AM77" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AN77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP77" t="s" s="2">
+      <c r="AQ77" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>84</v>
@@ -13214,10 +13211,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13243,13 +13240,13 @@
         <v>216</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -13278,11 +13275,11 @@
         <v>300</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>515</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
       </c>
@@ -13299,7 +13296,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -13323,27 +13320,27 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AP78" t="s" s="2">
+      <c r="AQ78" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AQ78" t="s" s="2">
+      <c r="AR78" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13464,10 +13461,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13590,10 +13587,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13616,19 +13613,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -13677,7 +13674,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13707,21 +13704,21 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR81" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AQ81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR81" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13747,16 +13744,16 @@
         <v>152</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13805,7 +13802,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13820,36 +13817,36 @@
         <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AL82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP82" t="s" s="2">
+      <c r="AQ82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR82" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR82" t="s" s="2">
-        <v>540</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13872,16 +13869,16 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13931,7 +13928,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13955,16 +13952,16 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>293</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>84</v>
@@ -13972,10 +13969,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13998,13 +13995,13 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -14055,7 +14052,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -14079,13 +14076,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP84" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -14096,10 +14093,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -14125,10 +14122,10 @@
         <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -14179,7 +14176,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -14209,7 +14206,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -14220,10 +14217,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14246,13 +14243,13 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -14303,7 +14300,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14327,13 +14324,13 @@
         <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14344,10 +14341,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14373,14 +14370,14 @@
         <v>185</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -14429,7 +14426,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14453,13 +14450,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14470,10 +14467,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14499,13 +14496,13 @@
         <v>216</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -14534,11 +14531,11 @@
         <v>300</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
       </c>
@@ -14555,7 +14552,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14585,7 +14582,7 @@
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14596,10 +14593,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14622,13 +14619,13 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14679,7 +14676,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14703,13 +14700,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14720,10 +14717,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14746,13 +14743,13 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14803,7 +14800,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14818,22 +14815,22 @@
         <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AL90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AO90" t="s" s="2">
+      <c r="AP90" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14844,10 +14841,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14870,16 +14867,16 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -14929,7 +14926,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14953,13 +14950,13 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP91" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14970,10 +14967,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -15094,10 +15091,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -15220,14 +15217,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -15249,10 +15246,10 @@
         <v>138</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>181</v>
@@ -15307,7 +15304,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -15348,10 +15345,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15374,17 +15371,17 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15433,7 +15430,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15463,21 +15460,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15503,14 +15500,14 @@
         <v>152</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -15559,7 +15556,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15574,36 +15571,36 @@
         <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR96" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>619</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15629,16 +15626,16 @@
         <v>216</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15666,28 +15663,28 @@
         <v>300</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="Z97" t="s" s="2">
+      <c r="AA97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15717,21 +15714,21 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15757,10 +15754,10 @@
         <v>152</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -15811,7 +15808,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15841,21 +15838,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15878,19 +15875,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15939,7 +15936,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15969,7 +15966,7 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15980,10 +15977,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -16104,10 +16101,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16230,14 +16227,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16259,10 +16256,10 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>181</v>
@@ -16317,7 +16314,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -16358,10 +16355,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16384,17 +16381,17 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16443,7 +16440,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16473,7 +16470,7 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -16484,10 +16481,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16510,17 +16507,17 @@
         <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -16569,37 +16566,37 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="AG104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
+      <c r="AK104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP104" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -16610,10 +16607,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16734,10 +16731,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16860,10 +16857,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16886,13 +16883,13 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -16943,7 +16940,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16973,7 +16970,7 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16984,10 +16981,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -17010,19 +17007,19 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -17071,7 +17068,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -17101,7 +17098,7 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -17112,10 +17109,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17138,13 +17135,13 @@
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -17195,7 +17192,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -17225,7 +17222,7 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -17236,10 +17233,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17262,19 +17259,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -17323,7 +17320,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17353,7 +17350,7 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -17364,10 +17361,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17390,19 +17387,19 @@
         <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="M111" t="s" s="2">
-        <v>688</v>
-      </c>
       <c r="N111" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O111" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17451,7 +17448,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -17481,7 +17478,7 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -17492,10 +17489,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17521,10 +17518,10 @@
         <v>113</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -17554,28 +17551,28 @@
         <v>209</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="Z112" t="s" s="2">
+      <c r="AA112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17605,7 +17602,7 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -17616,10 +17613,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17642,13 +17639,13 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17656,52 +17653,52 @@
         <v>84</v>
       </c>
       <c r="Q113" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="R113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="R113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17731,7 +17728,7 @@
         <v>84</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17742,10 +17739,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17768,13 +17765,13 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17825,7 +17822,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17855,7 +17852,7 @@
         <v>84</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17866,10 +17863,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17892,13 +17889,13 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17949,7 +17946,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17979,7 +17976,7 @@
         <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17990,10 +17987,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18016,13 +18013,13 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -18073,7 +18070,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -18103,7 +18100,7 @@
         <v>84</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -18114,10 +18111,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18143,10 +18140,10 @@
         <v>113</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -18176,11 +18173,11 @@
         <v>209</v>
       </c>
       <c r="Y117" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="Z117" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="Z117" t="s" s="2">
-        <v>694</v>
-      </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
       </c>
@@ -18197,7 +18194,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -18227,7 +18224,7 @@
         <v>84</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -18238,10 +18235,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18267,13 +18264,13 @@
         <v>113</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -18303,25 +18300,25 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -18362,10 +18359,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18388,16 +18385,16 @@
         <v>94</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -18447,7 +18444,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -18488,10 +18485,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18517,16 +18514,16 @@
         <v>113</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -18554,28 +18551,28 @@
         <v>209</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="Z120" t="s" s="2">
+      <c r="AA120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -18605,7 +18602,7 @@
         <v>84</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -18616,10 +18613,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18642,13 +18639,13 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>738</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18699,7 +18696,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18729,7 +18726,7 @@
         <v>84</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18740,10 +18737,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18769,13 +18766,13 @@
         <v>216</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>744</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -18804,28 +18801,28 @@
         <v>117</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="Z122" t="s" s="2">
+      <c r="AA122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18855,7 +18852,7 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18866,10 +18863,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18990,10 +18987,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -19116,10 +19113,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19142,19 +19139,19 @@
         <v>94</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -19203,7 +19200,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -19233,21 +19230,21 @@
         <v>84</v>
       </c>
       <c r="AP125" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR125" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR125" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19273,16 +19270,16 @@
         <v>152</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19331,7 +19328,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19346,14 +19343,14 @@
         <v>105</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AL126" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="AL126" t="s" s="2">
+      <c r="AM126" t="s" s="2">
         <v>756</v>
       </c>
-      <c r="AM126" t="s" s="2">
-        <v>757</v>
-      </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
       </c>
@@ -19361,21 +19358,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR126" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR126" t="s" s="2">
-        <v>540</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19398,16 +19395,16 @@
         <v>94</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -19436,28 +19433,28 @@
         <v>300</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="Z127" t="s" s="2">
+      <c r="AA127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF127" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19487,21 +19484,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AQ127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR127" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="AQ127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR127" t="s" s="2">
-        <v>767</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19527,16 +19524,16 @@
         <v>216</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19564,28 +19561,28 @@
         <v>300</v>
       </c>
       <c r="Y128" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="Z128" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="Z128" t="s" s="2">
+      <c r="AA128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF128" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19615,21 +19612,21 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="AQ128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR128" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="AQ128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR128" t="s" s="2">
-        <v>777</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19655,14 +19652,14 @@
         <v>216</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19690,28 +19687,28 @@
         <v>300</v>
       </c>
       <c r="Y129" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="Z129" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="Z129" t="s" s="2">
+      <c r="AA129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19741,21 +19738,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR129" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="AQ129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR129" t="s" s="2">
-        <v>786</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19876,10 +19873,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -20002,10 +19999,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -20028,19 +20025,19 @@
         <v>94</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -20089,7 +20086,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -20119,21 +20116,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AQ132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR132" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AQ132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR132" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20159,16 +20156,16 @@
         <v>152</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -20217,7 +20214,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20232,14 +20229,14 @@
         <v>105</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="AM133" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="AM133" t="s" s="2">
-        <v>793</v>
-      </c>
       <c r="AN133" t="s" s="2">
         <v>84</v>
       </c>
@@ -20247,21 +20244,21 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AQ133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR133" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AQ133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR133" t="s" s="2">
-        <v>540</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20287,16 +20284,16 @@
         <v>216</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>796</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20324,28 +20321,28 @@
         <v>300</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>799</v>
       </c>
-      <c r="Z134" t="s" s="2">
+      <c r="AA134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF134" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20375,21 +20372,21 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AQ134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR134" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="AQ134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR134" t="s" s="2">
-        <v>803</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20412,13 +20409,13 @@
         <v>94</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -20469,7 +20466,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20505,15 +20502,15 @@
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20634,10 +20631,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20760,10 +20757,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20789,14 +20786,14 @@
         <v>216</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20824,28 +20821,28 @@
         <v>300</v>
       </c>
       <c r="Y138" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="Z138" t="s" s="2">
         <v>815</v>
       </c>
-      <c r="Z138" t="s" s="2">
+      <c r="AA138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF138" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20881,15 +20878,15 @@
         <v>84</v>
       </c>
       <c r="AR138" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20912,19 +20909,19 @@
         <v>94</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>820</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>84</v>
@@ -20961,7 +20958,7 @@
         <v>84</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
@@ -20971,7 +20968,7 @@
         <v>142</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -21001,24 +20998,24 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR139" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="C140" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>84</v>
@@ -21040,19 +21037,19 @@
         <v>94</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>84</v>
@@ -21101,7 +21098,7 @@
         <v>84</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>82</v>
@@ -21131,21 +21128,21 @@
         <v>84</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>831</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21266,10 +21263,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21392,13 +21389,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="C143" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>84</v>
@@ -21420,16 +21417,16 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>836</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="M143" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>838</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>839</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -21494,13 +21491,13 @@
         <v>144</v>
       </c>
       <c r="AK143" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="AL143" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="AL143" t="s" s="2">
+      <c r="AM143" t="s" s="2">
         <v>841</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>842</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>84</v>
@@ -21520,10 +21517,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="B144" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21546,19 +21543,19 @@
         <v>94</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>846</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>847</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>848</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>84</v>
@@ -21607,7 +21604,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21637,21 +21634,21 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AQ144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR144" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="AQ144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR144" t="s" s="2">
-        <v>851</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B145" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21677,20 +21674,20 @@
         <v>113</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q145" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="P145" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q145" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="R145" t="s" s="2">
         <v>84</v>
@@ -21714,28 +21711,28 @@
         <v>209</v>
       </c>
       <c r="Y145" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="Z145" t="s" s="2">
         <v>858</v>
       </c>
-      <c r="Z145" t="s" s="2">
+      <c r="AA145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF145" t="s" s="2">
         <v>859</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>860</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21765,21 +21762,21 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="AQ145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR145" t="s" s="2">
         <v>861</v>
-      </c>
-      <c r="AQ145" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR145" t="s" s="2">
-        <v>862</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="B146" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21805,14 +21802,14 @@
         <v>152</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21861,7 +21858,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21891,21 +21888,21 @@
         <v>84</v>
       </c>
       <c r="AP146" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR146" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="AQ146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR146" t="s" s="2">
-        <v>870</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="B147" t="s" s="2">
         <v>871</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>872</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21931,14 +21928,14 @@
         <v>107</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>84</v>
@@ -21987,16 +21984,16 @@
         <v>84</v>
       </c>
       <c r="AF147" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI147" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>105</v>
@@ -22017,21 +22014,21 @@
         <v>84</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AQ147" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="B148" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22057,16 +22054,16 @@
         <v>113</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>882</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>883</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>884</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>84</v>
@@ -22115,7 +22112,7 @@
         <v>84</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>82</v>
@@ -22145,21 +22142,21 @@
         <v>84</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="AQ148" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22182,19 +22179,19 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>888</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>889</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>890</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>84</v>
@@ -22243,7 +22240,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -22273,21 +22270,21 @@
         <v>84</v>
       </c>
       <c r="AP149" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="AQ149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR149" t="s" s="2">
         <v>894</v>
-      </c>
-      <c r="AQ149" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR149" t="s" s="2">
-        <v>895</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22310,19 +22307,19 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>897</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="M150" t="s" s="2">
         <v>898</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>899</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>900</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>901</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>84</v>
@@ -22371,7 +22368,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22401,21 +22398,21 @@
         <v>84</v>
       </c>
       <c r="AP150" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="AQ150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR150" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="AQ150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR150" t="s" s="2">
-        <v>904</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22438,19 +22435,19 @@
         <v>94</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>906</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>907</v>
       </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>908</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>84</v>
@@ -22499,7 +22496,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22529,7 +22526,7 @@
         <v>84</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
@@ -22540,10 +22537,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22566,17 +22563,17 @@
         <v>94</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>913</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>914</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>84</v>
@@ -22625,7 +22622,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22655,7 +22652,7 @@
         <v>84</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
@@ -22666,10 +22663,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22692,13 +22689,13 @@
         <v>84</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="L153" t="s" s="2">
         <v>918</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="M153" t="s" s="2">
         <v>919</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>920</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22749,7 +22746,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22776,10 +22773,10 @@
         <v>84</v>
       </c>
       <c r="AO153" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="AP153" t="s" s="2">
         <v>921</v>
-      </c>
-      <c r="AP153" t="s" s="2">
-        <v>922</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
@@ -22790,10 +22787,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22914,10 +22911,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23040,14 +23037,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -23069,10 +23066,10 @@
         <v>138</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>181</v>
@@ -23127,7 +23124,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -23168,10 +23165,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23194,16 +23191,16 @@
         <v>84</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>927</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>928</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>929</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -23253,7 +23250,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -23283,7 +23280,7 @@
         <v>84</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
@@ -23294,10 +23291,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23418,10 +23415,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23544,14 +23541,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -23573,10 +23570,10 @@
         <v>138</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>181</v>
@@ -23631,7 +23628,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23672,10 +23669,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23698,13 +23695,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>935</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>936</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23755,7 +23752,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23785,7 +23782,7 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>84</v>
@@ -23796,10 +23793,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23822,13 +23819,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="L162" t="s" s="2">
         <v>939</v>
       </c>
-      <c r="L162" t="s" s="2">
+      <c r="M162" t="s" s="2">
         <v>940</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>941</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23879,7 +23876,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23909,7 +23906,7 @@
         <v>84</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23920,10 +23917,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23946,13 +23943,13 @@
         <v>84</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>943</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>944</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>945</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -24003,7 +24000,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -24033,7 +24030,7 @@
         <v>84</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>84</v>
@@ -24044,10 +24041,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24073,16 +24070,16 @@
         <v>254</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>947</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>948</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>949</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>950</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>84</v>
@@ -24131,7 +24128,7 @@
         <v>84</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -24158,10 +24155,10 @@
         <v>84</v>
       </c>
       <c r="AO164" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="AP164" t="s" s="2">
         <v>951</v>
-      </c>
-      <c r="AP164" t="s" s="2">
-        <v>952</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>84</v>
@@ -24172,10 +24169,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24198,16 +24195,16 @@
         <v>84</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>954</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>955</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>956</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -24257,7 +24254,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24284,24 +24281,24 @@
         <v>84</v>
       </c>
       <c r="AO165" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="AP165" t="s" s="2">
         <v>957</v>
       </c>
-      <c r="AP165" t="s" s="2">
+      <c r="AQ165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR165" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AQ165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR165" t="s" s="2">
-        <v>959</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24324,13 +24321,13 @@
         <v>84</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>961</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>962</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24381,7 +24378,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>82</v>
@@ -24408,24 +24405,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
+        <v>962</v>
+      </c>
+      <c r="AP166" t="s" s="2">
         <v>963</v>
       </c>
-      <c r="AP166" t="s" s="2">
+      <c r="AQ166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR166" t="s" s="2">
         <v>964</v>
-      </c>
-      <c r="AQ166" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR166" t="s" s="2">
-        <v>965</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24448,16 +24445,16 @@
         <v>84</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>967</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>968</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>969</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24507,7 +24504,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24534,10 +24531,10 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="AP167" t="s" s="2">
         <v>970</v>
-      </c>
-      <c r="AP167" t="s" s="2">
-        <v>971</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
@@ -24548,10 +24545,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24577,10 +24574,10 @@
         <v>262</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>973</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>974</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24631,7 +24628,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24661,10 +24658,10 @@
         <v>84</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>84</v>
@@ -24672,10 +24669,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24698,13 +24695,13 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>977</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>978</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -24755,7 +24752,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24782,10 +24779,10 @@
         <v>84</v>
       </c>
       <c r="AO169" t="s" s="2">
+        <v>978</v>
+      </c>
+      <c r="AP169" t="s" s="2">
         <v>979</v>
-      </c>
-      <c r="AP169" t="s" s="2">
-        <v>980</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24796,10 +24793,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24920,10 +24917,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25046,14 +25043,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -25075,10 +25072,10 @@
         <v>138</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N172" t="s" s="2">
         <v>181</v>
@@ -25133,7 +25130,7 @@
         <v>84</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>82</v>
@@ -25174,10 +25171,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25200,16 +25197,16 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>984</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>985</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>986</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>987</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -25238,11 +25235,11 @@
         <v>300</v>
       </c>
       <c r="Y173" t="s" s="2">
+        <v>987</v>
+      </c>
+      <c r="Z173" t="s" s="2">
         <v>988</v>
       </c>
-      <c r="Z173" t="s" s="2">
-        <v>989</v>
-      </c>
       <c r="AA173" t="s" s="2">
         <v>84</v>
       </c>
@@ -25259,7 +25256,7 @@
         <v>84</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>93</v>
@@ -25286,24 +25283,24 @@
         <v>84</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AP173" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="AQ173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR173" t="s" s="2">
         <v>990</v>
-      </c>
-      <c r="AQ173" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR173" t="s" s="2">
-        <v>991</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25329,10 +25326,10 @@
         <v>216</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>992</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>993</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>994</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -25362,11 +25359,11 @@
         <v>300</v>
       </c>
       <c r="Y174" t="s" s="2">
+        <v>994</v>
+      </c>
+      <c r="Z174" t="s" s="2">
         <v>995</v>
       </c>
-      <c r="Z174" t="s" s="2">
-        <v>996</v>
-      </c>
       <c r="AA174" t="s" s="2">
         <v>84</v>
       </c>
@@ -25383,7 +25380,7 @@
         <v>84</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>82</v>
@@ -25410,24 +25407,24 @@
         <v>84</v>
       </c>
       <c r="AO174" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="AP174" t="s" s="2">
         <v>997</v>
       </c>
-      <c r="AP174" t="s" s="2">
+      <c r="AQ174" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR174" t="s" s="2">
         <v>998</v>
-      </c>
-      <c r="AQ174" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR174" t="s" s="2">
-        <v>999</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25450,13 +25447,13 @@
         <v>84</v>
       </c>
       <c r="K175" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L175" t="s" s="2">
         <v>1001</v>
       </c>
-      <c r="L175" t="s" s="2">
+      <c r="M175" t="s" s="2">
         <v>1002</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>1003</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -25507,7 +25504,7 @@
         <v>84</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>82</v>
@@ -25531,13 +25528,13 @@
         <v>84</v>
       </c>
       <c r="AN175" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="AO175" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="AP175" t="s" s="2">
         <v>1004</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="AP175" t="s" s="2">
-        <v>1005</v>
       </c>
       <c r="AQ175" t="s" s="2">
         <v>84</v>
@@ -25548,14 +25545,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -25574,16 +25571,16 @@
         <v>84</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>1007</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>1008</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>1009</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>1010</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>1011</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -25633,7 +25630,7 @@
         <v>84</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>82</v>
@@ -25663,7 +25660,7 @@
         <v>84</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="AQ176" t="s" s="2">
         <v>84</v>
@@ -25674,10 +25671,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25700,16 +25697,16 @@
         <v>84</v>
       </c>
       <c r="K177" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="L177" t="s" s="2">
         <v>1014</v>
       </c>
-      <c r="L177" t="s" s="2">
+      <c r="M177" t="s" s="2">
         <v>1015</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>1016</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>1017</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -25759,7 +25756,7 @@
         <v>84</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>82</v>
@@ -25783,13 +25780,13 @@
         <v>84</v>
       </c>
       <c r="AN177" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP177" t="s" s="2">
         <v>1018</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP177" t="s" s="2">
-        <v>1019</v>
       </c>
       <c r="AQ177" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVA.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVA.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
